--- a/MedCare_Clinic_MiniProject 2.xlsx
+++ b/MedCare_Clinic_MiniProject 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF4B198-1543-4386-8ED7-0A02835CE907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB34A21A-5FBA-41C5-AE9D-1C0255B7A1B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="749" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="749" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw Data" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5243" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5259" uniqueCount="807">
   <si>
     <t>MEDCARE CLINIC &amp; PHARMACY — PATIENT VISIT RECORDS 2023–2024</t>
   </si>
@@ -2523,13 +2523,40 @@
     <t>Find the Total Revenue of Each cities</t>
   </si>
   <si>
-    <t>year</t>
-  </si>
-  <si>
     <t>Year</t>
   </si>
   <si>
     <t>NO of Patients</t>
+  </si>
+  <si>
+    <t>Average bill per Visit</t>
+  </si>
+  <si>
+    <t>16/7/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Made a year column </t>
+  </si>
+  <si>
+    <t>Find how many patients have visited in each year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found the total Revenue of each Year </t>
+  </si>
+  <si>
+    <t>Find the average bill of each year</t>
+  </si>
+  <si>
+    <t>Numbers prescribed</t>
+  </si>
+  <si>
+    <t>Total Medicine Cost</t>
+  </si>
+  <si>
+    <t>Find out how many times the Medicines are prescribed</t>
+  </si>
+  <si>
+    <t>Find the total medicine cost</t>
   </si>
 </sst>
 </file>
@@ -2881,7 +2908,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2956,52 +2983,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3019,13 +3000,62 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3782,7 +3812,7 @@
     <tableColumn id="13" xr3:uid="{9F7D5FA9-31CE-490F-AB9D-EC67F47EF023}" name="Revenue" dataDxfId="1">
       <calculatedColumnFormula>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{125FD900-7F9E-49C6-BE22-D6AA62765D6C}" name="year" dataDxfId="0">
+    <tableColumn id="14" xr3:uid="{125FD900-7F9E-49C6-BE22-D6AA62765D6C}" name="Year" dataDxfId="0">
       <calculatedColumnFormula>YEAR(Table2[[#This Row],[Visit Date]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3986,20 +4016,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
     </row>
     <row r="2" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -16210,7 +16240,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C9BF44B-4B3F-48E9-8418-077718AF102D}">
-  <dimension ref="B1:O311"/>
+  <dimension ref="B1:T311"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.28515625" customWidth="1"/>
@@ -16224,2960 +16254,3290 @@
     <col min="11" max="11" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:15" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="47" t="s">
+    <row r="1" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:20" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="32" t="s">
         <v>783</v>
       </c>
-      <c r="D2" s="49" t="s">
+      <c r="D2" s="33" t="s">
         <v>784</v>
       </c>
-      <c r="F2" s="47" t="s">
+      <c r="F2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="49" t="s">
+      <c r="G2" s="33" t="s">
         <v>786</v>
       </c>
-      <c r="I2" s="47" t="s">
+      <c r="I2" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="48" t="s">
+      <c r="J2" s="32" t="s">
         <v>791</v>
       </c>
-      <c r="K2" s="49" t="s">
+      <c r="K2" s="33" t="s">
         <v>792</v>
       </c>
-      <c r="M2" s="42" t="s">
+      <c r="M2" s="31" t="s">
+        <v>795</v>
+      </c>
+      <c r="N2" s="32" t="s">
         <v>796</v>
       </c>
-      <c r="N2" s="42" t="s">
+      <c r="O2" s="32" t="s">
+        <v>792</v>
+      </c>
+      <c r="P2" s="33" t="s">
         <v>797</v>
       </c>
-      <c r="O2" s="42" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B3" s="50" t="str" cm="1">
+      <c r="R2" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="S2" s="32" t="s">
+        <v>803</v>
+      </c>
+      <c r="T2" s="33" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B3" s="34" t="str" cm="1">
         <f t="array" ref="B3:B7">_xlfn.UNIQUE(Table2[Department])</f>
         <v>Cardiology</v>
       </c>
-      <c r="C3" s="51">
+      <c r="C3">
         <f>COUNTIF(Table2[Department],B3)</f>
         <v>85</v>
       </c>
-      <c r="D3" s="52">
+      <c r="D3" s="35">
         <f>SUMIF(Table2[Department],B3,Table2[Revenue])</f>
         <v>129030</v>
       </c>
-      <c r="F3" s="50" t="str" cm="1">
+      <c r="F3" s="34" t="str" cm="1">
         <f t="array" ref="F3:F311">_xlfn.UNIQUE(Table2[Patient Name2])</f>
         <v>Aarav Murugan</v>
       </c>
-      <c r="G3" s="52">
+      <c r="G3" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F3,Table2[Revenue])</f>
         <v>1340</v>
       </c>
-      <c r="I3" s="50" t="str" cm="1">
+      <c r="I3" s="34" t="str" cm="1">
         <f t="array" ref="I3:I8">_xlfn.UNIQUE(Table2[City])</f>
         <v>Chennai</v>
       </c>
-      <c r="J3" s="51">
+      <c r="J3">
         <f>COUNTIF(Table2[City],I3)</f>
         <v>91</v>
       </c>
-      <c r="K3" s="52">
+      <c r="K3" s="35">
         <f>SUMIF(Table2[City],I3,Table2[Revenue])</f>
         <v>96620</v>
       </c>
-      <c r="M3" cm="1">
-        <f t="array" ref="M3:M4">_xlfn.UNIQUE(Table2[year])</f>
+      <c r="M3" s="34" cm="1">
+        <f t="array" ref="M3:M4">_xlfn.UNIQUE(Table2[Year])</f>
         <v>2024</v>
       </c>
-      <c r="N3">
-        <f>COUNTIF(Table2[year],M3)</f>
+      <c r="N3" s="56">
+        <f>COUNTIF(Table2[Year],M3)</f>
         <v>165</v>
       </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="50" t="str">
+      <c r="O3" s="56">
+        <f>SUMIF(Table2[Year],M3,Table2[Revenue])</f>
+        <v>171840</v>
+      </c>
+      <c r="P3" s="35">
+        <f>AVERAGEIF(Table2[Year],M3,Table2[Revenue])</f>
+        <v>1041.4545454545455</v>
+      </c>
+      <c r="R3" s="34" t="str" cm="1">
+        <f t="array" ref="R3:R29">_xlfn.UNIQUE(Table2[Medicine Prescribed])</f>
+        <v>Clopidogrel</v>
+      </c>
+      <c r="S3" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R3)</f>
+        <v>18</v>
+      </c>
+      <c r="T3" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R3,Table2[Medicine Cost (₹)])</f>
+        <v>11410</v>
+      </c>
+    </row>
+    <row r="4" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="34" t="str">
         <v>Pediatrics</v>
       </c>
-      <c r="C4" s="51">
+      <c r="C4">
         <f>COUNTIF(Table2[Department],B4)</f>
         <v>43</v>
       </c>
-      <c r="D4" s="52">
+      <c r="D4" s="35">
         <f>SUMIF(Table2[Department],B4,Table2[Revenue])</f>
         <v>32200</v>
       </c>
-      <c r="F4" s="50" t="str">
+      <c r="F4" s="34" t="str">
         <v>Bhavya Murugan</v>
       </c>
-      <c r="G4" s="52">
+      <c r="G4" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F4,Table2[Revenue])</f>
         <v>1620</v>
       </c>
-      <c r="I4" s="50" t="str">
+      <c r="I4" s="34" t="str">
         <v>Trichy</v>
       </c>
-      <c r="J4" s="51">
+      <c r="J4">
         <f>COUNTIF(Table2[City],I4)</f>
         <v>53</v>
       </c>
-      <c r="K4" s="52">
+      <c r="K4" s="35">
         <f>SUMIF(Table2[City],I4,Table2[Revenue])</f>
         <v>59980</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="36">
         <v>2023</v>
       </c>
-      <c r="N4">
-        <f>COUNTIF(Table2[year],M4)</f>
+      <c r="N4" s="37">
+        <f>COUNTIF(Table2[Year],M4)</f>
         <v>155</v>
       </c>
-    </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B5" s="50" t="str">
+      <c r="O4" s="37">
+        <f>SUMIF(Table2[Year],M4,Table2[Revenue])</f>
+        <v>162670</v>
+      </c>
+      <c r="P4" s="38">
+        <f>AVERAGEIF(Table2[Year],M4,Table2[Revenue])</f>
+        <v>1049.483870967742</v>
+      </c>
+      <c r="R4" s="34" t="str">
+        <v>Ramipril</v>
+      </c>
+      <c r="S4" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R4)</f>
+        <v>20</v>
+      </c>
+      <c r="T4" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R4,Table2[Medicine Cost (₹)])</f>
+        <v>10970</v>
+      </c>
+    </row>
+    <row r="5" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B5" s="34" t="str">
         <v>Orthopedics</v>
       </c>
-      <c r="C5" s="51">
+      <c r="C5">
         <f>COUNTIF(Table2[Department],B5)</f>
         <v>51</v>
       </c>
-      <c r="D5" s="52">
+      <c r="D5" s="35">
         <f>SUMIF(Table2[Department],B5,Table2[Revenue])</f>
         <v>61820</v>
       </c>
-      <c r="F5" s="50" t="str">
+      <c r="F5" s="34" t="str">
         <v>Chirag Menon</v>
       </c>
-      <c r="G5" s="52">
+      <c r="G5" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F5,Table2[Revenue])</f>
         <v>720</v>
       </c>
-      <c r="I5" s="50" t="str">
+      <c r="I5" s="34" t="str">
         <v>Coimbatore</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5">
         <f>COUNTIF(Table2[City],I5)</f>
         <v>66</v>
       </c>
-      <c r="K5" s="52">
+      <c r="K5" s="35">
         <f>SUMIF(Table2[City],I5,Table2[Revenue])</f>
         <v>63050</v>
       </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B6" s="50" t="str">
+      <c r="R5" s="34" t="str">
+        <v>Amoxicillin Syrup</v>
+      </c>
+      <c r="S5" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R5)</f>
+        <v>13</v>
+      </c>
+      <c r="T5" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R5,Table2[Medicine Cost (₹)])</f>
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="6" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B6" s="34" t="str">
         <v>General Medicine</v>
       </c>
-      <c r="C6" s="51">
+      <c r="C6">
         <f>COUNTIF(Table2[Department],B6)</f>
         <v>87</v>
       </c>
-      <c r="D6" s="52">
+      <c r="D6" s="35">
         <f>SUMIF(Table2[Department],B6,Table2[Revenue])</f>
         <v>55110</v>
       </c>
-      <c r="F6" s="50" t="str">
+      <c r="F6" s="34" t="str">
         <v>Deepa Pandian</v>
       </c>
-      <c r="G6" s="52">
+      <c r="G6" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F6,Table2[Revenue])</f>
         <v>1230</v>
       </c>
-      <c r="I6" s="50" t="str">
+      <c r="I6" s="34" t="str">
         <v>Salem</v>
       </c>
-      <c r="J6" s="51">
+      <c r="J6">
         <f>COUNTIF(Table2[City],I6)</f>
         <v>36</v>
       </c>
-      <c r="K6" s="52">
+      <c r="K6" s="35">
         <f>SUMIF(Table2[City],I6,Table2[Revenue])</f>
         <v>35010</v>
       </c>
-    </row>
-    <row r="7" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="53" t="str">
+      <c r="R6" s="34" t="str">
+        <v>Diclofenac</v>
+      </c>
+      <c r="S6" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R6)</f>
+        <v>8</v>
+      </c>
+      <c r="T6" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R6,Table2[Medicine Cost (₹)])</f>
+        <v>3910</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="36" t="str">
         <v>Dermatology</v>
       </c>
-      <c r="C7" s="54">
+      <c r="C7" s="37">
         <f>COUNTIF(Table2[Department],B7)</f>
         <v>54</v>
       </c>
-      <c r="D7" s="55">
+      <c r="D7" s="38">
         <f>SUMIF(Table2[Department],B7,Table2[Revenue])</f>
         <v>56350</v>
       </c>
-      <c r="F7" s="50" t="str">
+      <c r="F7" s="34" t="str">
         <v>Elan Iyer</v>
       </c>
-      <c r="G7" s="52">
+      <c r="G7" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F7,Table2[Revenue])</f>
         <v>795</v>
       </c>
-      <c r="I7" s="50" t="str">
+      <c r="I7" s="34" t="str">
         <v>Madurai</v>
       </c>
-      <c r="J7" s="51">
+      <c r="J7">
         <f>COUNTIF(Table2[City],I7)</f>
         <v>49</v>
       </c>
-      <c r="K7" s="52">
+      <c r="K7" s="35">
         <f>SUMIF(Table2[City],I7,Table2[Revenue])</f>
         <v>54170</v>
       </c>
-    </row>
-    <row r="8" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F8" s="50" t="str">
+      <c r="R7" s="34" t="str">
+        <v>Ciprofloxacin</v>
+      </c>
+      <c r="S7" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R7)</f>
+        <v>13</v>
+      </c>
+      <c r="T7" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R7,Table2[Medicine Cost (₹)])</f>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F8" s="34" t="str">
         <v>Fatima Rao</v>
       </c>
-      <c r="G8" s="52">
+      <c r="G8" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F8,Table2[Revenue])</f>
         <v>980</v>
       </c>
-      <c r="I8" s="53" t="str">
+      <c r="I8" s="36" t="str">
         <v>Tirunelveli</v>
       </c>
-      <c r="J8" s="54">
+      <c r="J8" s="37">
         <f>COUNTIF(Table2[City],I8)</f>
         <v>25</v>
       </c>
-      <c r="K8" s="55">
+      <c r="K8" s="38">
         <f>SUMIF(Table2[City],I8,Table2[Revenue])</f>
         <v>25680</v>
       </c>
-    </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="F9" s="50" t="str">
+      <c r="R8" s="34" t="str">
+        <v>Cetirizine</v>
+      </c>
+      <c r="S8" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R8)</f>
+        <v>12</v>
+      </c>
+      <c r="T8" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R8,Table2[Medicine Cost (₹)])</f>
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="F9" s="34" t="str">
         <v>Ganesh Rao</v>
       </c>
-      <c r="G9" s="52">
+      <c r="G9" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F9,Table2[Revenue])</f>
         <v>860</v>
       </c>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="F10" s="50" t="str">
+      <c r="R9" s="34" t="str">
+        <v>Fluconazole</v>
+      </c>
+      <c r="S9" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R9)</f>
+        <v>12</v>
+      </c>
+      <c r="T9" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R9,Table2[Medicine Cost (₹)])</f>
+        <v>4730</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="F10" s="34" t="str">
         <v>Heena Pillai</v>
       </c>
-      <c r="G10" s="52">
+      <c r="G10" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F10,Table2[Revenue])</f>
         <v>890</v>
       </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="F11" s="50" t="str">
+      <c r="R10" s="34" t="str">
+        <v>Paracetamol Syrup</v>
+      </c>
+      <c r="S10" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R10)</f>
+        <v>10</v>
+      </c>
+      <c r="T10" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R10,Table2[Medicine Cost (₹)])</f>
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="F11" s="34" t="str">
         <v>Ishaan Reddy</v>
       </c>
-      <c r="G11" s="52">
+      <c r="G11" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F11,Table2[Revenue])</f>
         <v>1670</v>
       </c>
-    </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="F12" s="50" t="str">
+      <c r="R11" s="34" t="str">
+        <v>Atorvastatin</v>
+      </c>
+      <c r="S11" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R11)</f>
+        <v>13</v>
+      </c>
+      <c r="T11" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R11,Table2[Medicine Cost (₹)])</f>
+        <v>6780</v>
+      </c>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="F12" s="34" t="str">
         <v>Jasmine Singh</v>
       </c>
-      <c r="G12" s="52">
+      <c r="G12" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F12,Table2[Revenue])</f>
         <v>540</v>
       </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="F13" s="50" t="str">
+      <c r="R12" s="34" t="str">
+        <v>Amoxicillin</v>
+      </c>
+      <c r="S12" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R12)</f>
+        <v>11</v>
+      </c>
+      <c r="T12" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R12,Table2[Medicine Cost (₹)])</f>
+        <v>2960</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="F13" s="34" t="str">
         <v>Karthik Vel</v>
       </c>
-      <c r="G13" s="52">
+      <c r="G13" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F13,Table2[Revenue])</f>
         <v>1250</v>
       </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="F14" s="50" t="str">
+      <c r="R13" s="34" t="str">
+        <v>Calcium Tablets</v>
+      </c>
+      <c r="S13" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R13)</f>
+        <v>7</v>
+      </c>
+      <c r="T13" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R13,Table2[Medicine Cost (₹)])</f>
+        <v>2580</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="F14" s="34" t="str">
         <v>Lavanya Murugan</v>
       </c>
-      <c r="G14" s="52">
+      <c r="G14" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F14,Table2[Revenue])</f>
         <v>1200</v>
       </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="F15" s="50" t="str">
+      <c r="R14" s="34" t="str">
+        <v>Muscle Relaxant</v>
+      </c>
+      <c r="S14" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R14)</f>
+        <v>11</v>
+      </c>
+      <c r="T14" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R14,Table2[Medicine Cost (₹)])</f>
+        <v>3840</v>
+      </c>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="F15" s="34" t="str">
         <v>Mohan Rajan</v>
       </c>
-      <c r="G15" s="52">
+      <c r="G15" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F15,Table2[Revenue])</f>
         <v>830</v>
       </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="F16" s="50" t="str">
+      <c r="R15" s="34" t="str">
+        <v>Iron Tablets</v>
+      </c>
+      <c r="S15" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R15)</f>
+        <v>13</v>
+      </c>
+      <c r="T15" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R15,Table2[Medicine Cost (₹)])</f>
+        <v>2930</v>
+      </c>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="F16" s="34" t="str">
         <v>Nisha Mani</v>
       </c>
-      <c r="G16" s="52">
+      <c r="G16" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F16,Table2[Revenue])</f>
         <v>750</v>
       </c>
-    </row>
-    <row r="17" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F17" s="50" t="str">
+      <c r="R16" s="34" t="str">
+        <v>Pantoprazole</v>
+      </c>
+      <c r="S16" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R16)</f>
+        <v>13</v>
+      </c>
+      <c r="T16" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R16,Table2[Medicine Cost (₹)])</f>
+        <v>3170</v>
+      </c>
+    </row>
+    <row r="17" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F17" s="34" t="str">
         <v>Omkar Raja</v>
       </c>
-      <c r="G17" s="52">
+      <c r="G17" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F17,Table2[Revenue])</f>
         <v>995</v>
       </c>
-    </row>
-    <row r="18" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F18" s="50" t="str">
+      <c r="R17" s="34" t="str">
+        <v>Hydrocortisone</v>
+      </c>
+      <c r="S17" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R17)</f>
+        <v>10</v>
+      </c>
+      <c r="T17" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R17,Table2[Medicine Cost (₹)])</f>
+        <v>3530</v>
+      </c>
+    </row>
+    <row r="18" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F18" s="34" t="str">
         <v>Preethi Balan</v>
       </c>
-      <c r="G18" s="52">
+      <c r="G18" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F18,Table2[Revenue])</f>
         <v>1350</v>
       </c>
-    </row>
-    <row r="19" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F19" s="50" t="str">
+      <c r="R18" s="34" t="str">
+        <v>Salbutamol</v>
+      </c>
+      <c r="S18" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R18)</f>
+        <v>8</v>
+      </c>
+      <c r="T18" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R18,Table2[Medicine Cost (₹)])</f>
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="19" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F19" s="34" t="str">
         <v>Qasim Reddy</v>
       </c>
-      <c r="G19" s="52">
+      <c r="G19" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F19,Table2[Revenue])</f>
         <v>980</v>
       </c>
-    </row>
-    <row r="20" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F20" s="50" t="str">
+      <c r="R19" s="34" t="str">
+        <v>Clindamycin Gel</v>
+      </c>
+      <c r="S19" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R19)</f>
+        <v>11</v>
+      </c>
+      <c r="T19" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R19,Table2[Medicine Cost (₹)])</f>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="20" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F20" s="34" t="str">
         <v>Rekha Pandian</v>
       </c>
-      <c r="G20" s="52">
+      <c r="G20" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F20,Table2[Revenue])</f>
         <v>1190</v>
       </c>
-    </row>
-    <row r="21" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F21" s="50" t="str">
+      <c r="R20" s="34" t="str">
+        <v>Paracetamol</v>
+      </c>
+      <c r="S20" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R20)</f>
+        <v>8</v>
+      </c>
+      <c r="T20" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R20,Table2[Medicine Cost (₹)])</f>
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="21" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F21" s="34" t="str">
         <v>Sanjay Chandran</v>
       </c>
-      <c r="G21" s="52">
+      <c r="G21" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F21,Table2[Revenue])</f>
         <v>1330</v>
       </c>
-    </row>
-    <row r="22" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F22" s="50" t="str">
+      <c r="R21" s="34" t="str">
+        <v>Metformin</v>
+      </c>
+      <c r="S21" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R21)</f>
+        <v>17</v>
+      </c>
+      <c r="T21" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R21,Table2[Medicine Cost (₹)])</f>
+        <v>4040</v>
+      </c>
+    </row>
+    <row r="22" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F22" s="34" t="str">
         <v>Tanya Menon</v>
       </c>
-      <c r="G22" s="52">
+      <c r="G22" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F22,Table2[Revenue])</f>
         <v>1550</v>
       </c>
-    </row>
-    <row r="23" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F23" s="50" t="str">
+      <c r="R22" s="34" t="str">
+        <v>Ibuprofen</v>
+      </c>
+      <c r="S22" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R22)</f>
+        <v>16</v>
+      </c>
+      <c r="T22" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R22,Table2[Medicine Cost (₹)])</f>
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="23" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F23" s="34" t="str">
         <v>Uday Subramanian</v>
       </c>
-      <c r="G23" s="52">
+      <c r="G23" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F23,Table2[Revenue])</f>
         <v>930</v>
       </c>
-    </row>
-    <row r="24" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F24" s="50" t="str">
+      <c r="R23" s="34" t="str">
+        <v>Benzoyl Peroxide</v>
+      </c>
+      <c r="S23" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R23)</f>
+        <v>9</v>
+      </c>
+      <c r="T23" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R23,Table2[Medicine Cost (₹)])</f>
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="24" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F24" s="34" t="str">
         <v>Vimala Vel</v>
       </c>
-      <c r="G24" s="52">
+      <c r="G24" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F24,Table2[Revenue])</f>
         <v>1000</v>
       </c>
-    </row>
-    <row r="25" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F25" s="50" t="str">
+      <c r="R24" s="34" t="str">
+        <v>Aspirin</v>
+      </c>
+      <c r="S24" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R24)</f>
+        <v>24</v>
+      </c>
+      <c r="T24" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R24,Table2[Medicine Cost (₹)])</f>
+        <v>15130</v>
+      </c>
+    </row>
+    <row r="25" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F25" s="34" t="str">
         <v>Wasim Pandian</v>
       </c>
-      <c r="G25" s="52">
+      <c r="G25" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F25,Table2[Revenue])</f>
         <v>470</v>
       </c>
-    </row>
-    <row r="26" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F26" s="50" t="str">
+      <c r="R25" s="34" t="str">
+        <v>Vitamin D</v>
+      </c>
+      <c r="S25" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R25)</f>
+        <v>9</v>
+      </c>
+      <c r="T25" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R25,Table2[Medicine Cost (₹)])</f>
+        <v>4440</v>
+      </c>
+    </row>
+    <row r="26" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F26" s="34" t="str">
         <v>Xena Devi</v>
       </c>
-      <c r="G26" s="52">
+      <c r="G26" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F26,Table2[Revenue])</f>
         <v>650</v>
       </c>
-    </row>
-    <row r="27" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F27" s="50" t="str">
+      <c r="R26" s="34" t="str">
+        <v>Amlodipine</v>
+      </c>
+      <c r="S26" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R26)</f>
+        <v>12</v>
+      </c>
+      <c r="T26" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R26,Table2[Medicine Cost (₹)])</f>
+        <v>2910</v>
+      </c>
+    </row>
+    <row r="27" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F27" s="34" t="str">
         <v>Yogesh Menon</v>
       </c>
-      <c r="G27" s="52">
+      <c r="G27" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F27,Table2[Revenue])</f>
         <v>600</v>
       </c>
-    </row>
-    <row r="28" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F28" s="50" t="str">
+      <c r="R27" s="34" t="str">
+        <v>Metoprolol</v>
+      </c>
+      <c r="S27" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R27)</f>
+        <v>10</v>
+      </c>
+      <c r="T27" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R27,Table2[Medicine Cost (₹)])</f>
+        <v>5390</v>
+      </c>
+    </row>
+    <row r="28" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F28" s="34" t="str">
         <v>Zara Krishnan</v>
       </c>
-      <c r="G28" s="52">
+      <c r="G28" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F28,Table2[Revenue])</f>
         <v>1060</v>
       </c>
-    </row>
-    <row r="29" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F29" s="50" t="str">
+      <c r="R28" s="34" t="str">
+        <v>Acyclovir</v>
+      </c>
+      <c r="S28" s="56">
+        <f>COUNTIF(Table2[Medicine Prescribed],R28)</f>
+        <v>8</v>
+      </c>
+      <c r="T28" s="35">
+        <f>SUMIF(Table2[Medicine Prescribed],R28,Table2[Medicine Cost (₹)])</f>
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="29" spans="6:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F29" s="34" t="str">
         <v>Arjun Murugan</v>
       </c>
-      <c r="G29" s="52">
+      <c r="G29" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F29,Table2[Revenue])</f>
         <v>550</v>
       </c>
-    </row>
-    <row r="30" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F30" s="50" t="str">
+      <c r="R29" s="36" t="str">
+        <v>ORS Sachet</v>
+      </c>
+      <c r="S29" s="37">
+        <f>COUNTIF(Table2[Medicine Prescribed],R29)</f>
+        <v>4</v>
+      </c>
+      <c r="T29" s="38">
+        <f>SUMIF(Table2[Medicine Prescribed],R29,Table2[Medicine Cost (₹)])</f>
+        <v>980</v>
+      </c>
+    </row>
+    <row r="30" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F30" s="34" t="str">
         <v>Bhanu Mani</v>
       </c>
-      <c r="G30" s="52">
+      <c r="G30" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F30,Table2[Revenue])</f>
         <v>1320</v>
       </c>
     </row>
-    <row r="31" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F31" s="50" t="str">
+    <row r="31" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F31" s="34" t="str">
         <v>Chitra Menon</v>
       </c>
-      <c r="G31" s="52">
+      <c r="G31" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F31,Table2[Revenue])</f>
         <v>520</v>
       </c>
     </row>
-    <row r="32" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F32" s="50" t="str">
+    <row r="32" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="F32" s="34" t="str">
         <v>Dinesh Pillai</v>
       </c>
-      <c r="G32" s="52">
+      <c r="G32" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F32,Table2[Revenue])</f>
         <v>960</v>
       </c>
     </row>
     <row r="33" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F33" s="50" t="str">
+      <c r="F33" s="34" t="str">
         <v>Esha Narayanan</v>
       </c>
-      <c r="G33" s="52">
+      <c r="G33" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F33,Table2[Revenue])</f>
         <v>960</v>
       </c>
     </row>
     <row r="34" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F34" s="50" t="str">
+      <c r="F34" s="34" t="str">
         <v>Farhan Mani</v>
       </c>
-      <c r="G34" s="52">
+      <c r="G34" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F34,Table2[Revenue])</f>
         <v>1280</v>
       </c>
     </row>
     <row r="35" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F35" s="50" t="str">
+      <c r="F35" s="34" t="str">
         <v>Geetha Iyer</v>
       </c>
-      <c r="G35" s="52">
+      <c r="G35" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F35,Table2[Revenue])</f>
         <v>1600</v>
       </c>
     </row>
     <row r="36" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F36" s="50" t="str">
+      <c r="F36" s="34" t="str">
         <v>Harish Devi</v>
       </c>
-      <c r="G36" s="52">
+      <c r="G36" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F36,Table2[Revenue])</f>
         <v>820</v>
       </c>
     </row>
     <row r="37" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F37" s="50" t="str">
+      <c r="F37" s="34" t="str">
         <v>Indira Patel</v>
       </c>
-      <c r="G37" s="52">
+      <c r="G37" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F37,Table2[Revenue])</f>
         <v>1580</v>
       </c>
     </row>
     <row r="38" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F38" s="50" t="str">
+      <c r="F38" s="34" t="str">
         <v>Jaya Reddy</v>
       </c>
-      <c r="G38" s="52">
+      <c r="G38" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F38,Table2[Revenue])</f>
         <v>700</v>
       </c>
     </row>
     <row r="39" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F39" s="50" t="str">
+      <c r="F39" s="34" t="str">
         <v>Kiran Raja</v>
       </c>
-      <c r="G39" s="52">
+      <c r="G39" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F39,Table2[Revenue])</f>
         <v>1340</v>
       </c>
     </row>
     <row r="40" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F40" s="50" t="str">
+      <c r="F40" s="34" t="str">
         <v>Latha Rajan</v>
       </c>
-      <c r="G40" s="52">
+      <c r="G40" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F40,Table2[Revenue])</f>
         <v>1020</v>
       </c>
     </row>
     <row r="41" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F41" s="50" t="str">
+      <c r="F41" s="34" t="str">
         <v>Mani Mani</v>
       </c>
-      <c r="G41" s="52">
+      <c r="G41" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F41,Table2[Revenue])</f>
         <v>1130</v>
       </c>
     </row>
     <row r="42" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F42" s="50" t="str">
+      <c r="F42" s="34" t="str">
         <v>Nalini Reddy</v>
       </c>
-      <c r="G42" s="52">
+      <c r="G42" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F42,Table2[Revenue])</f>
         <v>760</v>
       </c>
     </row>
     <row r="43" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F43" s="50" t="str">
+      <c r="F43" s="34" t="str">
         <v>Pavan Chandran</v>
       </c>
-      <c r="G43" s="52">
+      <c r="G43" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F43,Table2[Revenue])</f>
         <v>670</v>
       </c>
     </row>
     <row r="44" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F44" s="50" t="str">
+      <c r="F44" s="34" t="str">
         <v>Radha Patel</v>
       </c>
-      <c r="G44" s="52">
+      <c r="G44" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F44,Table2[Revenue])</f>
         <v>660</v>
       </c>
     </row>
     <row r="45" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F45" s="50" t="str">
+      <c r="F45" s="34" t="str">
         <v>Suresh Murugan</v>
       </c>
-      <c r="G45" s="52">
+      <c r="G45" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F45,Table2[Revenue])</f>
         <v>1055</v>
       </c>
     </row>
     <row r="46" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F46" s="50" t="str">
+      <c r="F46" s="34" t="str">
         <v>Thilaga Sharma</v>
       </c>
-      <c r="G46" s="52">
+      <c r="G46" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F46,Table2[Revenue])</f>
         <v>750</v>
       </c>
     </row>
     <row r="47" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F47" s="50" t="str">
+      <c r="F47" s="34" t="str">
         <v>Usha Singh</v>
       </c>
-      <c r="G47" s="52">
+      <c r="G47" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F47,Table2[Revenue])</f>
         <v>690</v>
       </c>
     </row>
     <row r="48" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F48" s="50" t="str">
+      <c r="F48" s="34" t="str">
         <v>Venkat Balan</v>
       </c>
-      <c r="G48" s="52">
+      <c r="G48" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F48,Table2[Revenue])</f>
         <v>850</v>
       </c>
     </row>
     <row r="49" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F49" s="50" t="str">
+      <c r="F49" s="34" t="str">
         <v>Yamini Kumar</v>
       </c>
-      <c r="G49" s="52">
+      <c r="G49" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F49,Table2[Revenue])</f>
         <v>630</v>
       </c>
     </row>
     <row r="50" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F50" s="50" t="str">
+      <c r="F50" s="34" t="str">
         <v>Aditya Subramanian</v>
       </c>
-      <c r="G50" s="52">
+      <c r="G50" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F50,Table2[Revenue])</f>
         <v>760</v>
       </c>
     </row>
     <row r="51" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F51" s="50" t="str">
+      <c r="F51" s="34" t="str">
         <v>Bharathi Menon</v>
       </c>
-      <c r="G51" s="52">
+      <c r="G51" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F51,Table2[Revenue])</f>
         <v>1160</v>
       </c>
     </row>
     <row r="52" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F52" s="50" t="str">
+      <c r="F52" s="34" t="str">
         <v>Chandru Krishnan</v>
       </c>
-      <c r="G52" s="52">
+      <c r="G52" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F52,Table2[Revenue])</f>
         <v>1790</v>
       </c>
     </row>
     <row r="53" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F53" s="50" t="str">
+      <c r="F53" s="34" t="str">
         <v>Devika Balan</v>
       </c>
-      <c r="G53" s="52">
+      <c r="G53" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F53,Table2[Revenue])</f>
         <v>830</v>
       </c>
     </row>
     <row r="54" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F54" s="50" t="str">
+      <c r="F54" s="34" t="str">
         <v>Elango Reddy</v>
       </c>
-      <c r="G54" s="52">
+      <c r="G54" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F54,Table2[Revenue])</f>
         <v>1450</v>
       </c>
     </row>
     <row r="55" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F55" s="50" t="str">
+      <c r="F55" s="34" t="str">
         <v>Fathima Narayanan</v>
       </c>
-      <c r="G55" s="52">
+      <c r="G55" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F55,Table2[Revenue])</f>
         <v>1170</v>
       </c>
     </row>
     <row r="56" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F56" s="50" t="str">
+      <c r="F56" s="34" t="str">
         <v>Gopal Rajan</v>
       </c>
-      <c r="G56" s="52">
+      <c r="G56" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F56,Table2[Revenue])</f>
         <v>460</v>
       </c>
     </row>
     <row r="57" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F57" s="50" t="str">
+      <c r="F57" s="34" t="str">
         <v>Hema Menon</v>
       </c>
-      <c r="G57" s="52">
+      <c r="G57" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F57,Table2[Revenue])</f>
         <v>690</v>
       </c>
     </row>
     <row r="58" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F58" s="50" t="str">
+      <c r="F58" s="34" t="str">
         <v>Ilango Pandian</v>
       </c>
-      <c r="G58" s="52">
+      <c r="G58" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F58,Table2[Revenue])</f>
         <v>890</v>
       </c>
     </row>
     <row r="59" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F59" s="50" t="str">
+      <c r="F59" s="34" t="str">
         <v>Janani Narayanan</v>
       </c>
-      <c r="G59" s="52">
+      <c r="G59" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F59,Table2[Revenue])</f>
         <v>1040</v>
       </c>
     </row>
     <row r="60" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F60" s="50" t="str">
+      <c r="F60" s="34" t="str">
         <v>Kabilan Sharma</v>
       </c>
-      <c r="G60" s="52">
+      <c r="G60" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F60,Table2[Revenue])</f>
         <v>770</v>
       </c>
     </row>
     <row r="61" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F61" s="50" t="str">
+      <c r="F61" s="34" t="str">
         <v>Lalitha Krishnan</v>
       </c>
-      <c r="G61" s="52">
+      <c r="G61" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F61,Table2[Revenue])</f>
         <v>590</v>
       </c>
     </row>
     <row r="62" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F62" s="50" t="str">
+      <c r="F62" s="34" t="str">
         <v>Muthu Pillai</v>
       </c>
-      <c r="G62" s="52">
+      <c r="G62" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F62,Table2[Revenue])</f>
         <v>1590</v>
       </c>
     </row>
     <row r="63" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F63" s="50" t="str">
+      <c r="F63" s="34" t="str">
         <v>Nandini Menon</v>
       </c>
-      <c r="G63" s="52">
+      <c r="G63" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F63,Table2[Revenue])</f>
         <v>1430</v>
       </c>
     </row>
     <row r="64" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F64" s="50" t="str">
+      <c r="F64" s="34" t="str">
         <v>Prakash Raja</v>
       </c>
-      <c r="G64" s="52">
+      <c r="G64" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F64,Table2[Revenue])</f>
         <v>1710</v>
       </c>
     </row>
     <row r="65" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F65" s="50" t="str">
+      <c r="F65" s="34" t="str">
         <v>Ramya Iyer</v>
       </c>
-      <c r="G65" s="52">
+      <c r="G65" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F65,Table2[Revenue])</f>
         <v>640</v>
       </c>
     </row>
     <row r="66" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F66" s="50" t="str">
+      <c r="F66" s="34" t="str">
         <v>Selvam Vel</v>
       </c>
-      <c r="G66" s="52">
+      <c r="G66" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F66,Table2[Revenue])</f>
         <v>1130</v>
       </c>
     </row>
     <row r="67" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F67" s="50" t="str">
+      <c r="F67" s="34" t="str">
         <v>Thenmozhi Narayanan</v>
       </c>
-      <c r="G67" s="52">
+      <c r="G67" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F67,Table2[Revenue])</f>
         <v>600</v>
       </c>
     </row>
     <row r="68" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F68" s="50" t="str">
+      <c r="F68" s="34" t="str">
         <v>Uma Pandian</v>
       </c>
-      <c r="G68" s="52">
+      <c r="G68" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F68,Table2[Revenue])</f>
         <v>790</v>
       </c>
     </row>
     <row r="69" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F69" s="50" t="str">
+      <c r="F69" s="34" t="str">
         <v>Vijaya Iyer</v>
       </c>
-      <c r="G69" s="52">
+      <c r="G69" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F69,Table2[Revenue])</f>
         <v>1100</v>
       </c>
     </row>
     <row r="70" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F70" s="50" t="str">
+      <c r="F70" s="34" t="str">
         <v>Anbu Rajan</v>
       </c>
-      <c r="G70" s="52">
+      <c r="G70" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F70,Table2[Revenue])</f>
         <v>1340</v>
       </c>
     </row>
     <row r="71" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F71" s="50" t="str">
+      <c r="F71" s="34" t="str">
         <v>Bala Mani</v>
       </c>
-      <c r="G71" s="52">
+      <c r="G71" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F71,Table2[Revenue])</f>
         <v>1620</v>
       </c>
     </row>
     <row r="72" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F72" s="50" t="str">
+      <c r="F72" s="34" t="str">
         <v>Chandra Iyer</v>
       </c>
-      <c r="G72" s="52">
+      <c r="G72" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F72,Table2[Revenue])</f>
         <v>1300</v>
       </c>
     </row>
     <row r="73" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F73" s="50" t="str">
+      <c r="F73" s="34" t="str">
         <v>Durai Sharma</v>
       </c>
-      <c r="G73" s="52">
+      <c r="G73" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F73,Table2[Revenue])</f>
         <v>570</v>
       </c>
     </row>
     <row r="74" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F74" s="50" t="str">
+      <c r="F74" s="34" t="str">
         <v>Ezhil Nair</v>
       </c>
-      <c r="G74" s="52">
+      <c r="G74" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F74,Table2[Revenue])</f>
         <v>520</v>
       </c>
     </row>
     <row r="75" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F75" s="50" t="str">
+      <c r="F75" s="34" t="str">
         <v>Guna Kumar</v>
       </c>
-      <c r="G75" s="52">
+      <c r="G75" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F75,Table2[Revenue])</f>
         <v>1150</v>
       </c>
     </row>
     <row r="76" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F76" s="50" t="str">
+      <c r="F76" s="34" t="str">
         <v>Hari Iyer</v>
       </c>
-      <c r="G76" s="52">
+      <c r="G76" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F76,Table2[Revenue])</f>
         <v>850</v>
       </c>
     </row>
     <row r="77" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F77" s="50" t="str">
+      <c r="F77" s="34" t="str">
         <v>Indu Chandran</v>
       </c>
-      <c r="G77" s="52">
+      <c r="G77" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F77,Table2[Revenue])</f>
         <v>1350</v>
       </c>
     </row>
     <row r="78" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F78" s="50" t="str">
+      <c r="F78" s="34" t="str">
         <v>Jothi Mani</v>
       </c>
-      <c r="G78" s="52">
+      <c r="G78" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F78,Table2[Revenue])</f>
         <v>1180</v>
       </c>
     </row>
     <row r="79" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F79" s="50" t="str">
+      <c r="F79" s="34" t="str">
         <v>Kamal Subramanian</v>
       </c>
-      <c r="G79" s="52">
+      <c r="G79" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F79,Table2[Revenue])</f>
         <v>470</v>
       </c>
     </row>
     <row r="80" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F80" s="50" t="str">
+      <c r="F80" s="34" t="str">
         <v>Lekha Reddy</v>
       </c>
-      <c r="G80" s="52">
+      <c r="G80" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F80,Table2[Revenue])</f>
         <v>1160</v>
       </c>
     </row>
     <row r="81" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F81" s="50" t="str">
+      <c r="F81" s="34" t="str">
         <v>Malar Subramanian</v>
       </c>
-      <c r="G81" s="52">
+      <c r="G81" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F81,Table2[Revenue])</f>
         <v>1450</v>
       </c>
     </row>
     <row r="82" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F82" s="50" t="str">
+      <c r="F82" s="34" t="str">
         <v>Naga Selvam</v>
       </c>
-      <c r="G82" s="52">
+      <c r="G82" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F82,Table2[Revenue])</f>
         <v>900</v>
       </c>
     </row>
     <row r="83" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F83" s="50" t="str">
+      <c r="F83" s="34" t="str">
         <v>Oviya Reddy</v>
       </c>
-      <c r="G83" s="52">
+      <c r="G83" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F83,Table2[Revenue])</f>
         <v>590</v>
       </c>
     </row>
     <row r="84" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F84" s="50" t="str">
+      <c r="F84" s="34" t="str">
         <v>Pari Pillai</v>
       </c>
-      <c r="G84" s="52">
+      <c r="G84" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F84,Table2[Revenue])</f>
         <v>850</v>
       </c>
     </row>
     <row r="85" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F85" s="50" t="str">
+      <c r="F85" s="34" t="str">
         <v>Raja Verma</v>
       </c>
-      <c r="G85" s="52">
+      <c r="G85" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F85,Table2[Revenue])</f>
         <v>1530</v>
       </c>
     </row>
     <row r="86" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F86" s="50" t="str">
+      <c r="F86" s="34" t="str">
         <v>Suba Pandian</v>
       </c>
-      <c r="G86" s="52">
+      <c r="G86" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F86,Table2[Revenue])</f>
         <v>1020</v>
       </c>
     </row>
     <row r="87" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F87" s="50" t="str">
+      <c r="F87" s="34" t="str">
         <v>Tamil Kumar</v>
       </c>
-      <c r="G87" s="52">
+      <c r="G87" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F87,Table2[Revenue])</f>
         <v>760</v>
       </c>
     </row>
     <row r="88" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F88" s="50" t="str">
+      <c r="F88" s="34" t="str">
         <v>Vani Murugan</v>
       </c>
-      <c r="G88" s="52">
+      <c r="G88" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F88,Table2[Revenue])</f>
         <v>730</v>
       </c>
     </row>
     <row r="89" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F89" s="50" t="str">
+      <c r="F89" s="34" t="str">
         <v>Yamuna Patel</v>
       </c>
-      <c r="G89" s="52">
+      <c r="G89" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F89,Table2[Revenue])</f>
         <v>1770</v>
       </c>
     </row>
     <row r="90" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F90" s="50" t="str">
+      <c r="F90" s="34" t="str">
         <v>Abinaya Pillai</v>
       </c>
-      <c r="G90" s="52">
+      <c r="G90" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F90,Table2[Revenue])</f>
         <v>1650</v>
       </c>
     </row>
     <row r="91" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F91" s="50" t="str">
+      <c r="F91" s="34" t="str">
         <v>Boopathi Rajan</v>
       </c>
-      <c r="G91" s="52">
+      <c r="G91" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F91,Table2[Revenue])</f>
         <v>1190</v>
       </c>
     </row>
     <row r="92" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F92" s="50" t="str">
+      <c r="F92" s="34" t="str">
         <v>Chelvi Murugan</v>
       </c>
-      <c r="G92" s="52">
+      <c r="G92" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F92,Table2[Revenue])</f>
         <v>690</v>
       </c>
     </row>
     <row r="93" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F93" s="50" t="str">
+      <c r="F93" s="34" t="str">
         <v>Deva Menon</v>
       </c>
-      <c r="G93" s="52">
+      <c r="G93" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F93,Table2[Revenue])</f>
         <v>950</v>
       </c>
     </row>
     <row r="94" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F94" s="50" t="str">
+      <c r="F94" s="34" t="str">
         <v>Elaya Sharma</v>
       </c>
-      <c r="G94" s="52">
+      <c r="G94" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F94,Table2[Revenue])</f>
         <v>1620</v>
       </c>
     </row>
     <row r="95" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F95" s="50" t="str">
+      <c r="F95" s="34" t="str">
         <v>Guru Selvam</v>
       </c>
-      <c r="G95" s="52">
+      <c r="G95" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F95,Table2[Revenue])</f>
         <v>550</v>
       </c>
     </row>
     <row r="96" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F96" s="50" t="str">
+      <c r="F96" s="34" t="str">
         <v>Haran Menon</v>
       </c>
-      <c r="G96" s="52">
+      <c r="G96" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F96,Table2[Revenue])</f>
         <v>1260</v>
       </c>
     </row>
     <row r="97" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F97" s="50" t="str">
+      <c r="F97" s="34" t="str">
         <v>Ilavarsi Narayanan</v>
       </c>
-      <c r="G97" s="52">
+      <c r="G97" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F97,Table2[Revenue])</f>
         <v>550</v>
       </c>
     </row>
     <row r="98" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F98" s="50" t="str">
+      <c r="F98" s="34" t="str">
         <v>Jeeva Singh</v>
       </c>
-      <c r="G98" s="52">
+      <c r="G98" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F98,Table2[Revenue])</f>
         <v>1450</v>
       </c>
     </row>
     <row r="99" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F99" s="50" t="str">
+      <c r="F99" s="34" t="str">
         <v>Kavi Balan</v>
       </c>
-      <c r="G99" s="52">
+      <c r="G99" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F99,Table2[Revenue])</f>
         <v>1580</v>
       </c>
     </row>
     <row r="100" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F100" s="50" t="str">
+      <c r="F100" s="34" t="str">
         <v>Bhavya Pillai</v>
       </c>
-      <c r="G100" s="52">
+      <c r="G100" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F100,Table2[Revenue])</f>
         <v>1550</v>
       </c>
     </row>
     <row r="101" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F101" s="50" t="str">
+      <c r="F101" s="34" t="str">
         <v>Chirag Krishnan</v>
       </c>
-      <c r="G101" s="52">
+      <c r="G101" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F101,Table2[Revenue])</f>
         <v>800</v>
       </c>
     </row>
     <row r="102" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F102" s="50" t="str">
+      <c r="F102" s="34" t="str">
         <v>Deepa Raja</v>
       </c>
-      <c r="G102" s="52">
+      <c r="G102" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F102,Table2[Revenue])</f>
         <v>790</v>
       </c>
     </row>
     <row r="103" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F103" s="50" t="str">
+      <c r="F103" s="34" t="str">
         <v>Elan Chandran</v>
       </c>
-      <c r="G103" s="52">
+      <c r="G103" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F103,Table2[Revenue])</f>
         <v>640</v>
       </c>
     </row>
     <row r="104" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F104" s="50" t="str">
+      <c r="F104" s="34" t="str">
         <v>Fatima Sharma</v>
       </c>
-      <c r="G104" s="52">
+      <c r="G104" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F104,Table2[Revenue])</f>
         <v>1200</v>
       </c>
     </row>
     <row r="105" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F105" s="50" t="str">
+      <c r="F105" s="34" t="str">
         <v>Ganesh Pillai</v>
       </c>
-      <c r="G105" s="52">
+      <c r="G105" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F105,Table2[Revenue])</f>
         <v>790</v>
       </c>
     </row>
     <row r="106" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F106" s="50" t="str">
+      <c r="F106" s="34" t="str">
         <v>Heena Vel</v>
       </c>
-      <c r="G106" s="52">
+      <c r="G106" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F106,Table2[Revenue])</f>
         <v>1050</v>
       </c>
     </row>
     <row r="107" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F107" s="50" t="str">
+      <c r="F107" s="34" t="str">
         <v>Ishaan Raja</v>
       </c>
-      <c r="G107" s="52">
+      <c r="G107" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F107,Table2[Revenue])</f>
         <v>680</v>
       </c>
     </row>
     <row r="108" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F108" s="50" t="str">
+      <c r="F108" s="34" t="str">
         <v>Jasmine Pandian</v>
       </c>
-      <c r="G108" s="52">
+      <c r="G108" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F108,Table2[Revenue])</f>
         <v>1850</v>
       </c>
     </row>
     <row r="109" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F109" s="50" t="str">
+      <c r="F109" s="34" t="str">
         <v>Lavanya Pillai</v>
       </c>
-      <c r="G109" s="52">
+      <c r="G109" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F109,Table2[Revenue])</f>
         <v>1320</v>
       </c>
     </row>
     <row r="110" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F110" s="50" t="str">
+      <c r="F110" s="34" t="str">
         <v>Mohan Pandian</v>
       </c>
-      <c r="G110" s="52">
+      <c r="G110" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F110,Table2[Revenue])</f>
         <v>1270</v>
       </c>
     </row>
     <row r="111" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F111" s="50" t="str">
+      <c r="F111" s="34" t="str">
         <v>Nisha Subramanian</v>
       </c>
-      <c r="G111" s="52">
+      <c r="G111" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F111,Table2[Revenue])</f>
         <v>1640</v>
       </c>
     </row>
     <row r="112" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F112" s="50" t="str">
+      <c r="F112" s="34" t="str">
         <v>Omkar Nair</v>
       </c>
-      <c r="G112" s="52">
+      <c r="G112" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F112,Table2[Revenue])</f>
         <v>1270</v>
       </c>
     </row>
     <row r="113" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F113" s="50" t="str">
+      <c r="F113" s="34" t="str">
         <v>Preethi Nair</v>
       </c>
-      <c r="G113" s="52">
+      <c r="G113" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F113,Table2[Revenue])</f>
         <v>1440</v>
       </c>
     </row>
     <row r="114" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F114" s="50" t="str">
+      <c r="F114" s="34" t="str">
         <v>Qasim Nair</v>
       </c>
-      <c r="G114" s="52">
+      <c r="G114" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F114,Table2[Revenue])</f>
         <v>1150</v>
       </c>
     </row>
     <row r="115" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F115" s="50" t="str">
+      <c r="F115" s="34" t="str">
         <v>Rekha Pillai</v>
       </c>
-      <c r="G115" s="52">
+      <c r="G115" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F115,Table2[Revenue])</f>
         <v>1160</v>
       </c>
     </row>
     <row r="116" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F116" s="50" t="str">
+      <c r="F116" s="34" t="str">
         <v>Sanjay Verma</v>
       </c>
-      <c r="G116" s="52">
+      <c r="G116" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F116,Table2[Revenue])</f>
         <v>580</v>
       </c>
     </row>
     <row r="117" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F117" s="50" t="str">
+      <c r="F117" s="34" t="str">
         <v>Tanya Iyer</v>
       </c>
-      <c r="G117" s="52">
+      <c r="G117" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F117,Table2[Revenue])</f>
         <v>665</v>
       </c>
     </row>
     <row r="118" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F118" s="50" t="str">
+      <c r="F118" s="34" t="str">
         <v>Uday Iyer</v>
       </c>
-      <c r="G118" s="52">
+      <c r="G118" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F118,Table2[Revenue])</f>
         <v>640</v>
       </c>
     </row>
     <row r="119" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F119" s="50" t="str">
+      <c r="F119" s="34" t="str">
         <v>Vimala Subramanian</v>
       </c>
-      <c r="G119" s="52">
+      <c r="G119" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F119,Table2[Revenue])</f>
         <v>1090</v>
       </c>
     </row>
     <row r="120" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F120" s="50" t="str">
+      <c r="F120" s="34" t="str">
         <v>Wasim Pillai</v>
       </c>
-      <c r="G120" s="52">
+      <c r="G120" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F120,Table2[Revenue])</f>
         <v>1090</v>
       </c>
     </row>
     <row r="121" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F121" s="50" t="str">
+      <c r="F121" s="34" t="str">
         <v>Xena Menon</v>
       </c>
-      <c r="G121" s="52">
+      <c r="G121" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F121,Table2[Revenue])</f>
         <v>750</v>
       </c>
     </row>
     <row r="122" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F122" s="50" t="str">
+      <c r="F122" s="34" t="str">
         <v>Yogesh Balan</v>
       </c>
-      <c r="G122" s="52">
+      <c r="G122" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F122,Table2[Revenue])</f>
         <v>740</v>
       </c>
     </row>
     <row r="123" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F123" s="50" t="str">
+      <c r="F123" s="34" t="str">
         <v>Zara Patel</v>
       </c>
-      <c r="G123" s="52">
+      <c r="G123" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F123,Table2[Revenue])</f>
         <v>1430</v>
       </c>
     </row>
     <row r="124" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F124" s="50" t="str">
+      <c r="F124" s="34" t="str">
         <v>Arjun Chandran</v>
       </c>
-      <c r="G124" s="52">
+      <c r="G124" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F124,Table2[Revenue])</f>
         <v>1060</v>
       </c>
     </row>
     <row r="125" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F125" s="50" t="str">
+      <c r="F125" s="34" t="str">
         <v>Bhanu Rao</v>
       </c>
-      <c r="G125" s="52">
+      <c r="G125" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F125,Table2[Revenue])</f>
         <v>1390</v>
       </c>
     </row>
     <row r="126" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F126" s="50" t="str">
+      <c r="F126" s="34" t="str">
         <v>Chitra Singh</v>
       </c>
-      <c r="G126" s="52">
+      <c r="G126" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F126,Table2[Revenue])</f>
         <v>1285</v>
       </c>
     </row>
     <row r="127" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F127" s="50" t="str">
+      <c r="F127" s="34" t="str">
         <v>Dinesh Nair</v>
       </c>
-      <c r="G127" s="52">
+      <c r="G127" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F127,Table2[Revenue])</f>
         <v>1550</v>
       </c>
     </row>
     <row r="128" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F128" s="50" t="str">
+      <c r="F128" s="34" t="str">
         <v>Esha Krishnan</v>
       </c>
-      <c r="G128" s="52">
+      <c r="G128" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F128,Table2[Revenue])</f>
         <v>510</v>
       </c>
     </row>
     <row r="129" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F129" s="50" t="str">
+      <c r="F129" s="34" t="str">
         <v>Farhan Iyer</v>
       </c>
-      <c r="G129" s="52">
+      <c r="G129" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F129,Table2[Revenue])</f>
         <v>1630</v>
       </c>
     </row>
     <row r="130" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F130" s="50" t="str">
+      <c r="F130" s="34" t="str">
         <v>Geetha Mani</v>
       </c>
-      <c r="G130" s="52">
+      <c r="G130" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F130,Table2[Revenue])</f>
         <v>1310</v>
       </c>
     </row>
     <row r="131" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F131" s="50" t="str">
+      <c r="F131" s="34" t="str">
         <v>Harish Reddy</v>
       </c>
-      <c r="G131" s="52">
+      <c r="G131" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F131,Table2[Revenue])</f>
         <v>1510</v>
       </c>
     </row>
     <row r="132" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F132" s="50" t="str">
+      <c r="F132" s="34" t="str">
         <v>Indira Rajan</v>
       </c>
-      <c r="G132" s="52">
+      <c r="G132" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F132,Table2[Revenue])</f>
         <v>1330</v>
       </c>
     </row>
     <row r="133" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F133" s="50" t="str">
+      <c r="F133" s="34" t="str">
         <v>Jaya Verma</v>
       </c>
-      <c r="G133" s="52">
+      <c r="G133" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F133,Table2[Revenue])</f>
         <v>1550</v>
       </c>
     </row>
     <row r="134" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F134" s="50" t="str">
+      <c r="F134" s="34" t="str">
         <v>Kiran Kumar</v>
       </c>
-      <c r="G134" s="52">
+      <c r="G134" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F134,Table2[Revenue])</f>
         <v>1175</v>
       </c>
     </row>
     <row r="135" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F135" s="50" t="str">
+      <c r="F135" s="34" t="str">
         <v>Latha Devi</v>
       </c>
-      <c r="G135" s="52">
+      <c r="G135" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F135,Table2[Revenue])</f>
         <v>1110</v>
       </c>
     </row>
     <row r="136" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F136" s="50" t="str">
+      <c r="F136" s="34" t="str">
         <v>Mani Sharma</v>
       </c>
-      <c r="G136" s="52">
+      <c r="G136" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F136,Table2[Revenue])</f>
         <v>1580</v>
       </c>
     </row>
     <row r="137" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F137" s="50" t="str">
+      <c r="F137" s="34" t="str">
         <v>Nalini Patel</v>
       </c>
-      <c r="G137" s="52">
+      <c r="G137" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F137,Table2[Revenue])</f>
         <v>590</v>
       </c>
     </row>
     <row r="138" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F138" s="50" t="str">
+      <c r="F138" s="34" t="str">
         <v>Pavan Menon</v>
       </c>
-      <c r="G138" s="52">
+      <c r="G138" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F138,Table2[Revenue])</f>
         <v>1800</v>
       </c>
     </row>
     <row r="139" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F139" s="50" t="str">
+      <c r="F139" s="34" t="str">
         <v>Radha Murugan</v>
       </c>
-      <c r="G139" s="52">
+      <c r="G139" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F139,Table2[Revenue])</f>
         <v>550</v>
       </c>
     </row>
     <row r="140" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F140" s="50" t="str">
+      <c r="F140" s="34" t="str">
         <v>Thilaga Patel</v>
       </c>
-      <c r="G140" s="52">
+      <c r="G140" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F140,Table2[Revenue])</f>
         <v>1110</v>
       </c>
     </row>
     <row r="141" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F141" s="50" t="str">
+      <c r="F141" s="34" t="str">
         <v>Usha Murugan</v>
       </c>
-      <c r="G141" s="52">
+      <c r="G141" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F141,Table2[Revenue])</f>
         <v>660</v>
       </c>
     </row>
     <row r="142" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F142" s="50" t="str">
+      <c r="F142" s="34" t="str">
         <v>Venkat Murugan</v>
       </c>
-      <c r="G142" s="52">
+      <c r="G142" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F142,Table2[Revenue])</f>
         <v>1240</v>
       </c>
     </row>
     <row r="143" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F143" s="50" t="str">
+      <c r="F143" s="34" t="str">
         <v>Yamini Subramanian</v>
       </c>
-      <c r="G143" s="52">
+      <c r="G143" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F143,Table2[Revenue])</f>
         <v>1530</v>
       </c>
     </row>
     <row r="144" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F144" s="50" t="str">
+      <c r="F144" s="34" t="str">
         <v>Aditya Krishnan</v>
       </c>
-      <c r="G144" s="52">
+      <c r="G144" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F144,Table2[Revenue])</f>
         <v>1330</v>
       </c>
     </row>
     <row r="145" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F145" s="50" t="str">
+      <c r="F145" s="34" t="str">
         <v>Bharathi Balan</v>
       </c>
-      <c r="G145" s="52">
+      <c r="G145" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F145,Table2[Revenue])</f>
         <v>1200</v>
       </c>
     </row>
     <row r="146" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F146" s="50" t="str">
+      <c r="F146" s="34" t="str">
         <v>Chandru Reddy</v>
       </c>
-      <c r="G146" s="52">
+      <c r="G146" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F146,Table2[Revenue])</f>
         <v>1680</v>
       </c>
     </row>
     <row r="147" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F147" s="50" t="str">
+      <c r="F147" s="34" t="str">
         <v>Devika Iyer</v>
       </c>
-      <c r="G147" s="52">
+      <c r="G147" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F147,Table2[Revenue])</f>
         <v>960</v>
       </c>
     </row>
     <row r="148" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F148" s="50" t="str">
+      <c r="F148" s="34" t="str">
         <v>Elango Sharma</v>
       </c>
-      <c r="G148" s="52">
+      <c r="G148" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F148,Table2[Revenue])</f>
         <v>820</v>
       </c>
     </row>
     <row r="149" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F149" s="50" t="str">
+      <c r="F149" s="34" t="str">
         <v>Fathima Krishnan</v>
       </c>
-      <c r="G149" s="52">
+      <c r="G149" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F149,Table2[Revenue])</f>
         <v>1550</v>
       </c>
     </row>
     <row r="150" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F150" s="50" t="str">
+      <c r="F150" s="34" t="str">
         <v>Gopal Vel</v>
       </c>
-      <c r="G150" s="52">
+      <c r="G150" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F150,Table2[Revenue])</f>
         <v>670</v>
       </c>
     </row>
     <row r="151" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F151" s="50" t="str">
+      <c r="F151" s="34" t="str">
         <v>Hema Murugan</v>
       </c>
-      <c r="G151" s="52">
+      <c r="G151" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F151,Table2[Revenue])</f>
         <v>660</v>
       </c>
     </row>
     <row r="152" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F152" s="50" t="str">
+      <c r="F152" s="34" t="str">
         <v>Ilango Narayanan</v>
       </c>
-      <c r="G152" s="52">
+      <c r="G152" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F152,Table2[Revenue])</f>
         <v>1100</v>
       </c>
     </row>
     <row r="153" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F153" s="50" t="str">
+      <c r="F153" s="34" t="str">
         <v>Janani Rao</v>
       </c>
-      <c r="G153" s="52">
+      <c r="G153" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F153,Table2[Revenue])</f>
         <v>510</v>
       </c>
     </row>
     <row r="154" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F154" s="50" t="str">
+      <c r="F154" s="34" t="str">
         <v>Kabilan Verma</v>
       </c>
-      <c r="G154" s="52">
+      <c r="G154" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F154,Table2[Revenue])</f>
         <v>700</v>
       </c>
     </row>
     <row r="155" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F155" s="50" t="str">
+      <c r="F155" s="34" t="str">
         <v>Lalitha Selvam</v>
       </c>
-      <c r="G155" s="52">
+      <c r="G155" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F155,Table2[Revenue])</f>
         <v>610</v>
       </c>
     </row>
     <row r="156" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F156" s="50" t="str">
+      <c r="F156" s="34" t="str">
         <v>Muthu Rao</v>
       </c>
-      <c r="G156" s="52">
+      <c r="G156" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F156,Table2[Revenue])</f>
         <v>850</v>
       </c>
     </row>
     <row r="157" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F157" s="50" t="str">
+      <c r="F157" s="34" t="str">
         <v>Nandini Selvam</v>
       </c>
-      <c r="G157" s="52">
+      <c r="G157" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F157,Table2[Revenue])</f>
         <v>1140</v>
       </c>
     </row>
     <row r="158" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F158" s="50" t="str">
+      <c r="F158" s="34" t="str">
         <v>Prakash Vel</v>
       </c>
-      <c r="G158" s="52">
+      <c r="G158" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F158,Table2[Revenue])</f>
         <v>610</v>
       </c>
     </row>
     <row r="159" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F159" s="50" t="str">
+      <c r="F159" s="34" t="str">
         <v>Ramya Verma</v>
       </c>
-      <c r="G159" s="52">
+      <c r="G159" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F159,Table2[Revenue])</f>
         <v>1480</v>
       </c>
     </row>
     <row r="160" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F160" s="50" t="str">
+      <c r="F160" s="34" t="str">
         <v>Selvam Nair</v>
       </c>
-      <c r="G160" s="52">
+      <c r="G160" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F160,Table2[Revenue])</f>
         <v>1200</v>
       </c>
     </row>
     <row r="161" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F161" s="50" t="str">
+      <c r="F161" s="34" t="str">
         <v>Thenmozhi Raja</v>
       </c>
-      <c r="G161" s="52">
+      <c r="G161" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F161,Table2[Revenue])</f>
         <v>1200</v>
       </c>
     </row>
     <row r="162" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F162" s="50" t="str">
+      <c r="F162" s="34" t="str">
         <v>Uma Vel</v>
       </c>
-      <c r="G162" s="52">
+      <c r="G162" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F162,Table2[Revenue])</f>
         <v>900</v>
       </c>
     </row>
     <row r="163" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F163" s="50" t="str">
+      <c r="F163" s="34" t="str">
         <v>Vijaya Patel</v>
       </c>
-      <c r="G163" s="52">
+      <c r="G163" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F163,Table2[Revenue])</f>
         <v>1580</v>
       </c>
     </row>
     <row r="164" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F164" s="50" t="str">
+      <c r="F164" s="34" t="str">
         <v>Anbu Menon</v>
       </c>
-      <c r="G164" s="52">
+      <c r="G164" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F164,Table2[Revenue])</f>
         <v>1260</v>
       </c>
     </row>
     <row r="165" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F165" s="50" t="str">
+      <c r="F165" s="34" t="str">
         <v>Bala Raja</v>
       </c>
-      <c r="G165" s="52">
+      <c r="G165" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F165,Table2[Revenue])</f>
         <v>1520</v>
       </c>
     </row>
     <row r="166" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F166" s="50" t="str">
+      <c r="F166" s="34" t="str">
         <v>Chandra Mani</v>
       </c>
-      <c r="G166" s="52">
+      <c r="G166" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F166,Table2[Revenue])</f>
         <v>1680</v>
       </c>
     </row>
     <row r="167" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F167" s="50" t="str">
+      <c r="F167" s="34" t="str">
         <v>Durai Raja</v>
       </c>
-      <c r="G167" s="52">
+      <c r="G167" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F167,Table2[Revenue])</f>
         <v>650</v>
       </c>
     </row>
     <row r="168" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F168" s="50" t="str">
+      <c r="F168" s="34" t="str">
         <v>Ezhil Rao</v>
       </c>
-      <c r="G168" s="52">
+      <c r="G168" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F168,Table2[Revenue])</f>
         <v>760</v>
       </c>
     </row>
     <row r="169" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F169" s="50" t="str">
+      <c r="F169" s="34" t="str">
         <v>Guna Murugan</v>
       </c>
-      <c r="G169" s="52">
+      <c r="G169" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F169,Table2[Revenue])</f>
         <v>1600</v>
       </c>
     </row>
     <row r="170" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F170" s="50" t="str">
+      <c r="F170" s="34" t="str">
         <v>Hari Verma</v>
       </c>
-      <c r="G170" s="52">
+      <c r="G170" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F170,Table2[Revenue])</f>
         <v>1630</v>
       </c>
     </row>
     <row r="171" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F171" s="50" t="str">
+      <c r="F171" s="34" t="str">
         <v>Indu Narayanan</v>
       </c>
-      <c r="G171" s="52">
+      <c r="G171" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F171,Table2[Revenue])</f>
         <v>1220</v>
       </c>
     </row>
     <row r="172" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F172" s="50" t="str">
+      <c r="F172" s="34" t="str">
         <v>Jothi Reddy</v>
       </c>
-      <c r="G172" s="52">
+      <c r="G172" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F172,Table2[Revenue])</f>
         <v>880</v>
       </c>
     </row>
     <row r="173" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F173" s="50" t="str">
+      <c r="F173" s="34" t="str">
         <v>Kamal Narayanan</v>
       </c>
-      <c r="G173" s="52">
+      <c r="G173" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F173,Table2[Revenue])</f>
         <v>1060</v>
       </c>
     </row>
     <row r="174" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F174" s="50" t="str">
+      <c r="F174" s="34" t="str">
         <v>Lekha Subramanian</v>
       </c>
-      <c r="G174" s="52">
+      <c r="G174" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F174,Table2[Revenue])</f>
         <v>780</v>
       </c>
     </row>
     <row r="175" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F175" s="50" t="str">
+      <c r="F175" s="34" t="str">
         <v>Malar Singh</v>
       </c>
-      <c r="G175" s="52">
+      <c r="G175" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F175,Table2[Revenue])</f>
         <v>1070</v>
       </c>
     </row>
     <row r="176" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F176" s="50" t="str">
+      <c r="F176" s="34" t="str">
         <v>Naga Reddy</v>
       </c>
-      <c r="G176" s="52">
+      <c r="G176" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F176,Table2[Revenue])</f>
         <v>500</v>
       </c>
     </row>
     <row r="177" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F177" s="50" t="str">
+      <c r="F177" s="34" t="str">
         <v>Oviya Rajan</v>
       </c>
-      <c r="G177" s="52">
+      <c r="G177" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F177,Table2[Revenue])</f>
         <v>1640</v>
       </c>
     </row>
     <row r="178" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F178" s="50" t="str">
+      <c r="F178" s="34" t="str">
         <v>Pari Verma</v>
       </c>
-      <c r="G178" s="52">
+      <c r="G178" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F178,Table2[Revenue])</f>
         <v>630</v>
       </c>
     </row>
     <row r="179" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F179" s="50" t="str">
+      <c r="F179" s="34" t="str">
         <v>Raja Mani</v>
       </c>
-      <c r="G179" s="52">
+      <c r="G179" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F179,Table2[Revenue])</f>
         <v>1390</v>
       </c>
     </row>
     <row r="180" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F180" s="50" t="str">
+      <c r="F180" s="34" t="str">
         <v>Suba Patel</v>
       </c>
-      <c r="G180" s="52">
+      <c r="G180" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F180,Table2[Revenue])</f>
         <v>640</v>
       </c>
     </row>
     <row r="181" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F181" s="50" t="str">
+      <c r="F181" s="34" t="str">
         <v>Tamil Chandran</v>
       </c>
-      <c r="G181" s="52">
+      <c r="G181" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F181,Table2[Revenue])</f>
         <v>980</v>
       </c>
     </row>
     <row r="182" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F182" s="50" t="str">
+      <c r="F182" s="34" t="str">
         <v>Vani Balan</v>
       </c>
-      <c r="G182" s="52">
+      <c r="G182" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F182,Table2[Revenue])</f>
         <v>670</v>
       </c>
     </row>
     <row r="183" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F183" s="50" t="str">
+      <c r="F183" s="34" t="str">
         <v>Yamuna Pillai</v>
       </c>
-      <c r="G183" s="52">
+      <c r="G183" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F183,Table2[Revenue])</f>
         <v>1750</v>
       </c>
     </row>
     <row r="184" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F184" s="50" t="str">
+      <c r="F184" s="34" t="str">
         <v>Abinaya Singh</v>
       </c>
-      <c r="G184" s="52">
+      <c r="G184" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F184,Table2[Revenue])</f>
         <v>820</v>
       </c>
     </row>
     <row r="185" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F185" s="50" t="str">
+      <c r="F185" s="34" t="str">
         <v>Boopathi Subramanian</v>
       </c>
-      <c r="G185" s="52">
+      <c r="G185" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F185,Table2[Revenue])</f>
         <v>1330</v>
       </c>
     </row>
     <row r="186" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F186" s="50" t="str">
+      <c r="F186" s="34" t="str">
         <v>Chelvi Verma</v>
       </c>
-      <c r="G186" s="52">
+      <c r="G186" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F186,Table2[Revenue])</f>
         <v>580</v>
       </c>
     </row>
     <row r="187" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F187" s="50" t="str">
+      <c r="F187" s="34" t="str">
         <v>Deva Subramanian</v>
       </c>
-      <c r="G187" s="52">
+      <c r="G187" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F187,Table2[Revenue])</f>
         <v>640</v>
       </c>
     </row>
     <row r="188" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F188" s="50" t="str">
+      <c r="F188" s="34" t="str">
         <v>Elaya Mani</v>
       </c>
-      <c r="G188" s="52">
+      <c r="G188" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F188,Table2[Revenue])</f>
         <v>1840</v>
       </c>
     </row>
     <row r="189" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F189" s="50" t="str">
+      <c r="F189" s="34" t="str">
         <v>Guru Pandian</v>
       </c>
-      <c r="G189" s="52">
+      <c r="G189" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F189,Table2[Revenue])</f>
         <v>660</v>
       </c>
     </row>
     <row r="190" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F190" s="50" t="str">
+      <c r="F190" s="34" t="str">
         <v>Haran Iyer</v>
       </c>
-      <c r="G190" s="52">
+      <c r="G190" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F190,Table2[Revenue])</f>
         <v>1550</v>
       </c>
     </row>
     <row r="191" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F191" s="50" t="str">
+      <c r="F191" s="34" t="str">
         <v>Ilavarsi Verma</v>
       </c>
-      <c r="G191" s="52">
+      <c r="G191" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F191,Table2[Revenue])</f>
         <v>1530</v>
       </c>
     </row>
     <row r="192" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F192" s="50" t="str">
+      <c r="F192" s="34" t="str">
         <v>Jeeva Murugan</v>
       </c>
-      <c r="G192" s="52">
+      <c r="G192" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F192,Table2[Revenue])</f>
         <v>1500</v>
       </c>
     </row>
     <row r="193" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F193" s="50" t="str">
+      <c r="F193" s="34" t="str">
         <v>Kavi Mani</v>
       </c>
-      <c r="G193" s="52">
+      <c r="G193" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F193,Table2[Revenue])</f>
         <v>750</v>
       </c>
     </row>
     <row r="194" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F194" s="50" t="str">
+      <c r="F194" s="34" t="str">
         <v>Aarav Mani</v>
       </c>
-      <c r="G194" s="52">
+      <c r="G194" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F194,Table2[Revenue])</f>
         <v>810</v>
       </c>
     </row>
     <row r="195" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F195" s="50" t="str">
+      <c r="F195" s="34" t="str">
         <v>Bhavya Pandian</v>
       </c>
-      <c r="G195" s="52">
+      <c r="G195" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F195,Table2[Revenue])</f>
         <v>1130</v>
       </c>
     </row>
     <row r="196" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F196" s="50" t="str">
+      <c r="F196" s="34" t="str">
         <v>Chirag Pandian</v>
       </c>
-      <c r="G196" s="52">
+      <c r="G196" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F196,Table2[Revenue])</f>
         <v>920</v>
       </c>
     </row>
     <row r="197" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F197" s="50" t="str">
+      <c r="F197" s="34" t="str">
         <v>Deepa Mani</v>
       </c>
-      <c r="G197" s="52">
+      <c r="G197" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F197,Table2[Revenue])</f>
         <v>1140</v>
       </c>
     </row>
     <row r="198" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F198" s="50" t="str">
+      <c r="F198" s="34" t="str">
         <v>Elan Raja</v>
       </c>
-      <c r="G198" s="52">
+      <c r="G198" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F198,Table2[Revenue])</f>
         <v>700</v>
       </c>
     </row>
     <row r="199" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F199" s="50" t="str">
+      <c r="F199" s="34" t="str">
         <v>Fatima Narayanan</v>
       </c>
-      <c r="G199" s="52">
+      <c r="G199" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F199,Table2[Revenue])</f>
         <v>860</v>
       </c>
     </row>
     <row r="200" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F200" s="50" t="str">
+      <c r="F200" s="34" t="str">
         <v>Ganesh Menon</v>
       </c>
-      <c r="G200" s="52">
+      <c r="G200" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F200,Table2[Revenue])</f>
         <v>1040</v>
       </c>
     </row>
     <row r="201" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F201" s="50" t="str">
+      <c r="F201" s="34" t="str">
         <v>Heena Murugan</v>
       </c>
-      <c r="G201" s="52">
+      <c r="G201" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F201,Table2[Revenue])</f>
         <v>810</v>
       </c>
     </row>
     <row r="202" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F202" s="50" t="str">
+      <c r="F202" s="34" t="str">
         <v>Ishaan Patel</v>
       </c>
-      <c r="G202" s="52">
+      <c r="G202" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F202,Table2[Revenue])</f>
         <v>1820</v>
       </c>
     </row>
     <row r="203" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F203" s="50" t="str">
+      <c r="F203" s="34" t="str">
         <v>Jasmine Menon</v>
       </c>
-      <c r="G203" s="52">
+      <c r="G203" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F203,Table2[Revenue])</f>
         <v>1180</v>
       </c>
     </row>
     <row r="204" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F204" s="50" t="str">
+      <c r="F204" s="34" t="str">
         <v>Karthik Krishnan</v>
       </c>
-      <c r="G204" s="52">
+      <c r="G204" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F204,Table2[Revenue])</f>
         <v>1450</v>
       </c>
     </row>
     <row r="205" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F205" s="50" t="str">
+      <c r="F205" s="34" t="str">
         <v>Lavanya Kumar</v>
       </c>
-      <c r="G205" s="52">
+      <c r="G205" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F205,Table2[Revenue])</f>
         <v>570</v>
       </c>
     </row>
     <row r="206" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F206" s="50" t="str">
+      <c r="F206" s="34" t="str">
         <v>Mohan Mani</v>
       </c>
-      <c r="G206" s="52">
+      <c r="G206" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F206,Table2[Revenue])</f>
         <v>1820</v>
       </c>
     </row>
     <row r="207" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F207" s="50" t="str">
+      <c r="F207" s="34" t="str">
         <v>Nisha Krishnan</v>
       </c>
-      <c r="G207" s="52">
+      <c r="G207" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F207,Table2[Revenue])</f>
         <v>1200</v>
       </c>
     </row>
     <row r="208" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F208" s="50" t="str">
+      <c r="F208" s="34" t="str">
         <v>Preethi Verma</v>
       </c>
-      <c r="G208" s="52">
+      <c r="G208" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F208,Table2[Revenue])</f>
         <v>970</v>
       </c>
     </row>
     <row r="209" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F209" s="50" t="str">
+      <c r="F209" s="34" t="str">
         <v>Qasim Menon</v>
       </c>
-      <c r="G209" s="52">
+      <c r="G209" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F209,Table2[Revenue])</f>
         <v>760</v>
       </c>
     </row>
     <row r="210" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F210" s="50" t="str">
+      <c r="F210" s="34" t="str">
         <v>Rekha Mani</v>
       </c>
-      <c r="G210" s="52">
+      <c r="G210" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F210,Table2[Revenue])</f>
         <v>810</v>
       </c>
     </row>
     <row r="211" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F211" s="50" t="str">
+      <c r="F211" s="34" t="str">
         <v>Sanjay Mani</v>
       </c>
-      <c r="G211" s="52">
+      <c r="G211" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F211,Table2[Revenue])</f>
         <v>720</v>
       </c>
     </row>
     <row r="212" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F212" s="50" t="str">
+      <c r="F212" s="34" t="str">
         <v>Uday Selvam</v>
       </c>
-      <c r="G212" s="52">
+      <c r="G212" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F212,Table2[Revenue])</f>
         <v>740</v>
       </c>
     </row>
     <row r="213" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F213" s="50" t="str">
+      <c r="F213" s="34" t="str">
         <v>Vimala Singh</v>
       </c>
-      <c r="G213" s="52">
+      <c r="G213" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F213,Table2[Revenue])</f>
         <v>760</v>
       </c>
     </row>
     <row r="214" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F214" s="50" t="str">
+      <c r="F214" s="34" t="str">
         <v>Wasim Mani</v>
       </c>
-      <c r="G214" s="52">
+      <c r="G214" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F214,Table2[Revenue])</f>
         <v>660</v>
       </c>
     </row>
     <row r="215" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F215" s="50" t="str">
+      <c r="F215" s="34" t="str">
         <v>Xena Subramanian</v>
       </c>
-      <c r="G215" s="52">
+      <c r="G215" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F215,Table2[Revenue])</f>
         <v>480</v>
       </c>
     </row>
     <row r="216" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F216" s="50" t="str">
+      <c r="F216" s="34" t="str">
         <v>Yogesh Vel</v>
       </c>
-      <c r="G216" s="52">
+      <c r="G216" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F216,Table2[Revenue])</f>
         <v>590</v>
       </c>
     </row>
     <row r="217" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F217" s="50" t="str">
+      <c r="F217" s="34" t="str">
         <v>Zara Raja</v>
       </c>
-      <c r="G217" s="52">
+      <c r="G217" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F217,Table2[Revenue])</f>
         <v>1020</v>
       </c>
     </row>
     <row r="218" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F218" s="50" t="str">
+      <c r="F218" s="34" t="str">
         <v>Arjun Rao</v>
       </c>
-      <c r="G218" s="52">
+      <c r="G218" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F218,Table2[Revenue])</f>
         <v>1250</v>
       </c>
     </row>
     <row r="219" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F219" s="50" t="str">
+      <c r="F219" s="34" t="str">
         <v>Bhanu Subramanian</v>
       </c>
-      <c r="G219" s="52">
+      <c r="G219" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F219,Table2[Revenue])</f>
         <v>1490</v>
       </c>
     </row>
     <row r="220" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F220" s="50" t="str">
+      <c r="F220" s="34" t="str">
         <v>Chitra Krishnan</v>
       </c>
-      <c r="G220" s="52">
+      <c r="G220" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F220,Table2[Revenue])</f>
         <v>1230</v>
       </c>
     </row>
     <row r="221" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F221" s="50" t="str">
+      <c r="F221" s="34" t="str">
         <v>Dinesh Mani</v>
       </c>
-      <c r="G221" s="52">
+      <c r="G221" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F221,Table2[Revenue])</f>
         <v>570</v>
       </c>
     </row>
     <row r="222" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F222" s="50" t="str">
+      <c r="F222" s="34" t="str">
         <v>Esha Murugan</v>
       </c>
-      <c r="G222" s="52">
+      <c r="G222" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F222,Table2[Revenue])</f>
         <v>1530</v>
       </c>
     </row>
     <row r="223" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F223" s="50" t="str">
+      <c r="F223" s="34" t="str">
         <v>Farhan Kumar</v>
       </c>
-      <c r="G223" s="52">
+      <c r="G223" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F223,Table2[Revenue])</f>
         <v>730</v>
       </c>
     </row>
     <row r="224" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F224" s="50" t="str">
+      <c r="F224" s="34" t="str">
         <v>Geetha Nair</v>
       </c>
-      <c r="G224" s="52">
+      <c r="G224" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F224,Table2[Revenue])</f>
         <v>840</v>
       </c>
     </row>
     <row r="225" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F225" s="50" t="str">
+      <c r="F225" s="34" t="str">
         <v>Harish Rajan</v>
       </c>
-      <c r="G225" s="52">
+      <c r="G225" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F225,Table2[Revenue])</f>
         <v>680</v>
       </c>
     </row>
     <row r="226" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F226" s="50" t="str">
+      <c r="F226" s="34" t="str">
         <v>Indira Balan</v>
       </c>
-      <c r="G226" s="52">
+      <c r="G226" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F226,Table2[Revenue])</f>
         <v>1400</v>
       </c>
     </row>
     <row r="227" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F227" s="50" t="str">
+      <c r="F227" s="34" t="str">
         <v>Jaya Menon</v>
       </c>
-      <c r="G227" s="52">
+      <c r="G227" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F227,Table2[Revenue])</f>
         <v>790</v>
       </c>
     </row>
     <row r="228" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F228" s="50" t="str">
+      <c r="F228" s="34" t="str">
         <v>Mani Verma</v>
       </c>
-      <c r="G228" s="52">
+      <c r="G228" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F228,Table2[Revenue])</f>
         <v>500</v>
       </c>
     </row>
     <row r="229" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F229" s="50" t="str">
+      <c r="F229" s="34" t="str">
         <v>Nalini Mani</v>
       </c>
-      <c r="G229" s="52">
+      <c r="G229" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F229,Table2[Revenue])</f>
         <v>690</v>
       </c>
     </row>
     <row r="230" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F230" s="50" t="str">
+      <c r="F230" s="34" t="str">
         <v>Pavan Vel</v>
       </c>
-      <c r="G230" s="52">
+      <c r="G230" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F230,Table2[Revenue])</f>
         <v>810</v>
       </c>
     </row>
     <row r="231" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F231" s="50" t="str">
+      <c r="F231" s="34" t="str">
         <v>Radha Iyer</v>
       </c>
-      <c r="G231" s="52">
+      <c r="G231" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F231,Table2[Revenue])</f>
         <v>1470</v>
       </c>
     </row>
     <row r="232" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F232" s="50" t="str">
+      <c r="F232" s="34" t="str">
         <v>Suresh Rajan</v>
       </c>
-      <c r="G232" s="52">
+      <c r="G232" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F232,Table2[Revenue])</f>
         <v>540</v>
       </c>
     </row>
     <row r="233" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F233" s="50" t="str">
+      <c r="F233" s="34" t="str">
         <v>Thilaga Narayanan</v>
       </c>
-      <c r="G233" s="52">
+      <c r="G233" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F233,Table2[Revenue])</f>
         <v>710</v>
       </c>
     </row>
     <row r="234" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F234" s="50" t="str">
+      <c r="F234" s="34" t="str">
         <v>Usha Menon</v>
       </c>
-      <c r="G234" s="52">
+      <c r="G234" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F234,Table2[Revenue])</f>
         <v>870</v>
       </c>
     </row>
     <row r="235" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F235" s="50" t="str">
+      <c r="F235" s="34" t="str">
         <v>Venkat Singh</v>
       </c>
-      <c r="G235" s="52">
+      <c r="G235" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F235,Table2[Revenue])</f>
         <v>420</v>
       </c>
     </row>
     <row r="236" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F236" s="50" t="str">
+      <c r="F236" s="34" t="str">
         <v>Yamini Vel</v>
       </c>
-      <c r="G236" s="52">
+      <c r="G236" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F236,Table2[Revenue])</f>
         <v>540</v>
       </c>
     </row>
     <row r="237" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F237" s="50" t="str">
+      <c r="F237" s="34" t="str">
         <v>Aditya Vel</v>
       </c>
-      <c r="G237" s="52">
+      <c r="G237" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F237,Table2[Revenue])</f>
         <v>1540</v>
       </c>
     </row>
     <row r="238" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F238" s="50" t="str">
+      <c r="F238" s="34" t="str">
         <v>Bharathi Subramanian</v>
       </c>
-      <c r="G238" s="52">
+      <c r="G238" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F238,Table2[Revenue])</f>
         <v>1030</v>
       </c>
     </row>
     <row r="239" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F239" s="50" t="str">
+      <c r="F239" s="34" t="str">
         <v>Chandru Narayanan</v>
       </c>
-      <c r="G239" s="52">
+      <c r="G239" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F239,Table2[Revenue])</f>
         <v>1580</v>
       </c>
     </row>
     <row r="240" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F240" s="50" t="str">
+      <c r="F240" s="34" t="str">
         <v>Elango Rajan</v>
       </c>
-      <c r="G240" s="52">
+      <c r="G240" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F240,Table2[Revenue])</f>
         <v>1400</v>
       </c>
     </row>
     <row r="241" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F241" s="50" t="str">
+      <c r="F241" s="34" t="str">
         <v>Fathima Selvam</v>
       </c>
-      <c r="G241" s="52">
+      <c r="G241" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F241,Table2[Revenue])</f>
         <v>880</v>
       </c>
     </row>
     <row r="242" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F242" s="50" t="str">
+      <c r="F242" s="34" t="str">
         <v>Gopal Pandian</v>
       </c>
-      <c r="G242" s="52">
+      <c r="G242" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F242,Table2[Revenue])</f>
         <v>740</v>
       </c>
     </row>
     <row r="243" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F243" s="50" t="str">
+      <c r="F243" s="34" t="str">
         <v>Hema Selvam</v>
       </c>
-      <c r="G243" s="52">
+      <c r="G243" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F243,Table2[Revenue])</f>
         <v>1040</v>
       </c>
     </row>
     <row r="244" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F244" s="50" t="str">
+      <c r="F244" s="34" t="str">
         <v>Janani Verma</v>
       </c>
-      <c r="G244" s="52">
+      <c r="G244" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F244,Table2[Revenue])</f>
         <v>1520</v>
       </c>
     </row>
     <row r="245" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F245" s="50" t="str">
+      <c r="F245" s="34" t="str">
         <v>Kabilan Menon</v>
       </c>
-      <c r="G245" s="52">
+      <c r="G245" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F245,Table2[Revenue])</f>
         <v>1490</v>
       </c>
     </row>
     <row r="246" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F246" s="50" t="str">
+      <c r="F246" s="34" t="str">
         <v>Lalitha Vel</v>
       </c>
-      <c r="G246" s="52">
+      <c r="G246" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F246,Table2[Revenue])</f>
         <v>660</v>
       </c>
     </row>
     <row r="247" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F247" s="50" t="str">
+      <c r="F247" s="34" t="str">
         <v>Muthu Kumar</v>
       </c>
-      <c r="G247" s="52">
+      <c r="G247" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F247,Table2[Revenue])</f>
         <v>880</v>
       </c>
     </row>
     <row r="248" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F248" s="50" t="str">
+      <c r="F248" s="34" t="str">
         <v>Nandini Nair</v>
       </c>
-      <c r="G248" s="52">
+      <c r="G248" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F248,Table2[Revenue])</f>
         <v>1490</v>
       </c>
     </row>
     <row r="249" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F249" s="50" t="str">
+      <c r="F249" s="34" t="str">
         <v>Prakash Verma</v>
       </c>
-      <c r="G249" s="52">
+      <c r="G249" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F249,Table2[Revenue])</f>
         <v>1250</v>
       </c>
     </row>
     <row r="250" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F250" s="50" t="str">
+      <c r="F250" s="34" t="str">
         <v>Ramya Reddy</v>
       </c>
-      <c r="G250" s="52">
+      <c r="G250" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F250,Table2[Revenue])</f>
         <v>460</v>
       </c>
     </row>
     <row r="251" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F251" s="50" t="str">
+      <c r="F251" s="34" t="str">
         <v>Selvam Devi</v>
       </c>
-      <c r="G251" s="52">
+      <c r="G251" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F251,Table2[Revenue])</f>
         <v>540</v>
       </c>
     </row>
     <row r="252" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F252" s="50" t="str">
+      <c r="F252" s="34" t="str">
         <v>Thenmozhi Sharma</v>
       </c>
-      <c r="G252" s="52">
+      <c r="G252" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F252,Table2[Revenue])</f>
         <v>1020</v>
       </c>
     </row>
     <row r="253" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F253" s="50" t="str">
+      <c r="F253" s="34" t="str">
         <v>Uma Sharma</v>
       </c>
-      <c r="G253" s="52">
+      <c r="G253" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F253,Table2[Revenue])</f>
         <v>450</v>
       </c>
     </row>
     <row r="254" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F254" s="50" t="str">
+      <c r="F254" s="34" t="str">
         <v>Vijaya Subramanian</v>
       </c>
-      <c r="G254" s="52">
+      <c r="G254" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F254,Table2[Revenue])</f>
         <v>1910</v>
       </c>
     </row>
     <row r="255" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F255" s="50" t="str">
+      <c r="F255" s="34" t="str">
         <v>Anbu Verma</v>
       </c>
-      <c r="G255" s="52">
+      <c r="G255" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F255,Table2[Revenue])</f>
         <v>1090</v>
       </c>
     </row>
     <row r="256" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F256" s="50" t="str">
+      <c r="F256" s="34" t="str">
         <v>Bala Krishnan</v>
       </c>
-      <c r="G256" s="52">
+      <c r="G256" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F256,Table2[Revenue])</f>
         <v>1830</v>
       </c>
     </row>
     <row r="257" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F257" s="50" t="str">
+      <c r="F257" s="34" t="str">
         <v>Chandra Balan</v>
       </c>
-      <c r="G257" s="52">
+      <c r="G257" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F257,Table2[Revenue])</f>
         <v>520</v>
       </c>
     </row>
     <row r="258" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F258" s="50" t="str">
+      <c r="F258" s="34" t="str">
         <v>Durai Selvam</v>
       </c>
-      <c r="G258" s="52">
+      <c r="G258" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F258,Table2[Revenue])</f>
         <v>510</v>
       </c>
     </row>
     <row r="259" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F259" s="50" t="str">
+      <c r="F259" s="34" t="str">
         <v>Ezhil Raja</v>
       </c>
-      <c r="G259" s="52">
+      <c r="G259" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F259,Table2[Revenue])</f>
         <v>1610</v>
       </c>
     </row>
     <row r="260" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F260" s="50" t="str">
+      <c r="F260" s="34" t="str">
         <v>Guna Devi</v>
       </c>
-      <c r="G260" s="52">
+      <c r="G260" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F260,Table2[Revenue])</f>
         <v>600</v>
       </c>
     </row>
     <row r="261" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F261" s="50" t="str">
+      <c r="F261" s="34" t="str">
         <v>Hari Devi</v>
       </c>
-      <c r="G261" s="52">
+      <c r="G261" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F261,Table2[Revenue])</f>
         <v>1100</v>
       </c>
     </row>
     <row r="262" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F262" s="50" t="str">
+      <c r="F262" s="34" t="str">
         <v>Indu Verma</v>
       </c>
-      <c r="G262" s="52">
+      <c r="G262" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F262,Table2[Revenue])</f>
         <v>1000</v>
       </c>
     </row>
     <row r="263" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F263" s="50" t="str">
+      <c r="F263" s="34" t="str">
         <v>Jothi Menon</v>
       </c>
-      <c r="G263" s="52">
+      <c r="G263" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F263,Table2[Revenue])</f>
         <v>1610</v>
       </c>
     </row>
     <row r="264" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F264" s="50" t="str">
+      <c r="F264" s="34" t="str">
         <v>Kamal Nair</v>
       </c>
-      <c r="G264" s="52">
+      <c r="G264" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F264,Table2[Revenue])</f>
         <v>1910</v>
       </c>
     </row>
     <row r="265" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F265" s="50" t="str">
+      <c r="F265" s="34" t="str">
         <v>Lekha Murugan</v>
       </c>
-      <c r="G265" s="52">
+      <c r="G265" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F265,Table2[Revenue])</f>
         <v>1480</v>
       </c>
     </row>
     <row r="266" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F266" s="50" t="str">
+      <c r="F266" s="34" t="str">
         <v>Malar Murugan</v>
       </c>
-      <c r="G266" s="52">
+      <c r="G266" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F266,Table2[Revenue])</f>
         <v>880</v>
       </c>
     </row>
     <row r="267" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F267" s="50" t="str">
+      <c r="F267" s="34" t="str">
         <v>Naga Iyer</v>
       </c>
-      <c r="G267" s="52">
+      <c r="G267" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F267,Table2[Revenue])</f>
         <v>1100</v>
       </c>
     </row>
     <row r="268" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F268" s="50" t="str">
+      <c r="F268" s="34" t="str">
         <v>Oviya Singh</v>
       </c>
-      <c r="G268" s="52">
+      <c r="G268" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F268,Table2[Revenue])</f>
         <v>540</v>
       </c>
     </row>
     <row r="269" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F269" s="50" t="str">
+      <c r="F269" s="34" t="str">
         <v>Pari Narayanan</v>
       </c>
-      <c r="G269" s="52">
+      <c r="G269" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F269,Table2[Revenue])</f>
         <v>1700</v>
       </c>
     </row>
     <row r="270" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F270" s="50" t="str">
+      <c r="F270" s="34" t="str">
         <v>Raja Patel</v>
       </c>
-      <c r="G270" s="52">
+      <c r="G270" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F270,Table2[Revenue])</f>
         <v>1160</v>
       </c>
     </row>
     <row r="271" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F271" s="50" t="str">
+      <c r="F271" s="34" t="str">
         <v>Suba Pillai</v>
       </c>
-      <c r="G271" s="52">
+      <c r="G271" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F271,Table2[Revenue])</f>
         <v>1100</v>
       </c>
     </row>
     <row r="272" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F272" s="50" t="str">
+      <c r="F272" s="34" t="str">
         <v>Tamil Pillai</v>
       </c>
-      <c r="G272" s="52">
+      <c r="G272" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F272,Table2[Revenue])</f>
         <v>840</v>
       </c>
     </row>
     <row r="273" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F273" s="50" t="str">
+      <c r="F273" s="34" t="str">
         <v>Vani Narayanan</v>
       </c>
-      <c r="G273" s="52">
+      <c r="G273" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F273,Table2[Revenue])</f>
         <v>660</v>
       </c>
     </row>
     <row r="274" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F274" s="50" t="str">
+      <c r="F274" s="34" t="str">
         <v>Yamuna Raja</v>
       </c>
-      <c r="G274" s="52">
+      <c r="G274" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F274,Table2[Revenue])</f>
         <v>1030</v>
       </c>
     </row>
     <row r="275" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F275" s="50" t="str">
+      <c r="F275" s="34" t="str">
         <v>Abinaya Raja</v>
       </c>
-      <c r="G275" s="52">
+      <c r="G275" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F275,Table2[Revenue])</f>
         <v>890</v>
       </c>
     </row>
     <row r="276" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F276" s="50" t="str">
+      <c r="F276" s="34" t="str">
         <v>Boopathi Murugan</v>
       </c>
-      <c r="G276" s="52">
+      <c r="G276" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F276,Table2[Revenue])</f>
         <v>710</v>
       </c>
     </row>
     <row r="277" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F277" s="50" t="str">
+      <c r="F277" s="34" t="str">
         <v>Chelvi Subramanian</v>
       </c>
-      <c r="G277" s="52">
+      <c r="G277" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F277,Table2[Revenue])</f>
         <v>1160</v>
       </c>
     </row>
     <row r="278" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F278" s="50" t="str">
+      <c r="F278" s="34" t="str">
         <v>Deva Balan</v>
       </c>
-      <c r="G278" s="52">
+      <c r="G278" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F278,Table2[Revenue])</f>
         <v>1030</v>
       </c>
     </row>
     <row r="279" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F279" s="50" t="str">
+      <c r="F279" s="34" t="str">
         <v>Elaya Raja</v>
       </c>
-      <c r="G279" s="52">
+      <c r="G279" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F279,Table2[Revenue])</f>
         <v>1090</v>
       </c>
     </row>
     <row r="280" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F280" s="50" t="str">
+      <c r="F280" s="34" t="str">
         <v>Guru Iyer</v>
       </c>
-      <c r="G280" s="52">
+      <c r="G280" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F280,Table2[Revenue])</f>
         <v>580</v>
       </c>
     </row>
     <row r="281" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F281" s="50" t="str">
+      <c r="F281" s="34" t="str">
         <v>Haran Krishnan</v>
       </c>
-      <c r="G281" s="52">
+      <c r="G281" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F281,Table2[Revenue])</f>
         <v>730</v>
       </c>
     </row>
     <row r="282" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F282" s="50" t="str">
+      <c r="F282" s="34" t="str">
         <v>Ilavarsi Singh</v>
       </c>
-      <c r="G282" s="52">
+      <c r="G282" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F282,Table2[Revenue])</f>
         <v>530</v>
       </c>
     </row>
     <row r="283" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F283" s="50" t="str">
+      <c r="F283" s="34" t="str">
         <v>Jeeva Menon</v>
       </c>
-      <c r="G283" s="52">
+      <c r="G283" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F283,Table2[Revenue])</f>
         <v>720</v>
       </c>
     </row>
     <row r="284" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F284" s="50" t="str">
+      <c r="F284" s="34" t="str">
         <v>Kavi Singh</v>
       </c>
-      <c r="G284" s="52">
+      <c r="G284" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F284,Table2[Revenue])</f>
         <v>1050</v>
       </c>
     </row>
     <row r="285" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F285" s="50" t="str">
+      <c r="F285" s="34" t="str">
         <v>Aarav Narayanan</v>
       </c>
-      <c r="G285" s="52">
+      <c r="G285" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F285,Table2[Revenue])</f>
         <v>1550</v>
       </c>
     </row>
     <row r="286" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F286" s="50" t="str">
+      <c r="F286" s="34" t="str">
         <v>Bhavya Devi</v>
       </c>
-      <c r="G286" s="52">
+      <c r="G286" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F286,Table2[Revenue])</f>
         <v>1180</v>
       </c>
     </row>
     <row r="287" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F287" s="50" t="str">
+      <c r="F287" s="34" t="str">
         <v>Chirag Raja</v>
       </c>
-      <c r="G287" s="52">
+      <c r="G287" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F287,Table2[Revenue])</f>
         <v>490</v>
       </c>
     </row>
     <row r="288" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F288" s="50" t="str">
+      <c r="F288" s="34" t="str">
         <v>Deepa Murugan</v>
       </c>
-      <c r="G288" s="52">
+      <c r="G288" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F288,Table2[Revenue])</f>
         <v>610</v>
       </c>
     </row>
     <row r="289" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F289" s="50" t="str">
+      <c r="F289" s="34" t="str">
         <v>Fatima Chandran</v>
       </c>
-      <c r="G289" s="52">
+      <c r="G289" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F289,Table2[Revenue])</f>
         <v>1180</v>
       </c>
     </row>
     <row r="290" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F290" s="50" t="str">
+      <c r="F290" s="34" t="str">
         <v>Ganesh Devi</v>
       </c>
-      <c r="G290" s="52">
+      <c r="G290" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F290,Table2[Revenue])</f>
         <v>570</v>
       </c>
     </row>
     <row r="291" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F291" s="50" t="str">
+      <c r="F291" s="34" t="str">
         <v>Heena Selvam</v>
       </c>
-      <c r="G291" s="52">
+      <c r="G291" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F291,Table2[Revenue])</f>
         <v>1120</v>
       </c>
     </row>
     <row r="292" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F292" s="50" t="str">
+      <c r="F292" s="34" t="str">
         <v>Ishaan Chandran</v>
       </c>
-      <c r="G292" s="52">
+      <c r="G292" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F292,Table2[Revenue])</f>
         <v>1360</v>
       </c>
     </row>
     <row r="293" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F293" s="50" t="str">
+      <c r="F293" s="34" t="str">
         <v>Jasmine Mani</v>
       </c>
-      <c r="G293" s="52">
+      <c r="G293" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F293,Table2[Revenue])</f>
         <v>730</v>
       </c>
     </row>
     <row r="294" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F294" s="50" t="str">
+      <c r="F294" s="34" t="str">
         <v>Karthik Iyer</v>
       </c>
-      <c r="G294" s="52">
+      <c r="G294" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F294,Table2[Revenue])</f>
         <v>690</v>
       </c>
     </row>
     <row r="295" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F295" s="50" t="str">
+      <c r="F295" s="34" t="str">
         <v>Lavanya Reddy</v>
       </c>
-      <c r="G295" s="52">
+      <c r="G295" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F295,Table2[Revenue])</f>
         <v>1060</v>
       </c>
     </row>
     <row r="296" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F296" s="50" t="str">
+      <c r="F296" s="34" t="str">
         <v>Mohan Balan</v>
       </c>
-      <c r="G296" s="52">
+      <c r="G296" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F296,Table2[Revenue])</f>
         <v>840</v>
       </c>
     </row>
     <row r="297" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F297" s="50" t="str">
+      <c r="F297" s="34" t="str">
         <v>Nisha Rao</v>
       </c>
-      <c r="G297" s="52">
+      <c r="G297" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F297,Table2[Revenue])</f>
         <v>900</v>
       </c>
     </row>
     <row r="298" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F298" s="50" t="str">
+      <c r="F298" s="34" t="str">
         <v>Omkar Narayanan</v>
       </c>
-      <c r="G298" s="52">
+      <c r="G298" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F298,Table2[Revenue])</f>
         <v>980</v>
       </c>
     </row>
     <row r="299" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F299" s="50" t="str">
+      <c r="F299" s="34" t="str">
         <v>Preethi Rajan</v>
       </c>
-      <c r="G299" s="52">
+      <c r="G299" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F299,Table2[Revenue])</f>
         <v>880</v>
       </c>
     </row>
     <row r="300" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F300" s="50" t="str">
+      <c r="F300" s="34" t="str">
         <v>Qasim Kumar</v>
       </c>
-      <c r="G300" s="52">
+      <c r="G300" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F300,Table2[Revenue])</f>
         <v>980</v>
       </c>
     </row>
     <row r="301" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F301" s="50" t="str">
+      <c r="F301" s="34" t="str">
         <v>Rekha Nair</v>
       </c>
-      <c r="G301" s="52">
+      <c r="G301" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F301,Table2[Revenue])</f>
         <v>1780</v>
       </c>
     </row>
     <row r="302" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F302" s="50" t="str">
+      <c r="F302" s="34" t="str">
         <v>Sanjay Patel</v>
       </c>
-      <c r="G302" s="52">
+      <c r="G302" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F302,Table2[Revenue])</f>
         <v>720</v>
       </c>
     </row>
     <row r="303" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F303" s="50" t="str">
+      <c r="F303" s="34" t="str">
         <v>Tanya Chandran</v>
       </c>
-      <c r="G303" s="52">
+      <c r="G303" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F303,Table2[Revenue])</f>
         <v>1340</v>
       </c>
     </row>
     <row r="304" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F304" s="50" t="str">
+      <c r="F304" s="34" t="str">
         <v>Uday Reddy</v>
       </c>
-      <c r="G304" s="52">
+      <c r="G304" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F304,Table2[Revenue])</f>
         <v>1800</v>
       </c>
     </row>
     <row r="305" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F305" s="50" t="str">
+      <c r="F305" s="34" t="str">
         <v>Vimala Patel</v>
       </c>
-      <c r="G305" s="52">
+      <c r="G305" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F305,Table2[Revenue])</f>
         <v>1250</v>
       </c>
     </row>
     <row r="306" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F306" s="50" t="str">
+      <c r="F306" s="34" t="str">
         <v>Wasim Selvam</v>
       </c>
-      <c r="G306" s="52">
+      <c r="G306" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F306,Table2[Revenue])</f>
         <v>1340</v>
       </c>
     </row>
     <row r="307" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F307" s="50" t="str">
+      <c r="F307" s="34" t="str">
         <v>Xena Vel</v>
       </c>
-      <c r="G307" s="52">
+      <c r="G307" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F307,Table2[Revenue])</f>
         <v>910</v>
       </c>
     </row>
     <row r="308" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F308" s="50" t="str">
+      <c r="F308" s="34" t="str">
         <v>Yogesh Kumar</v>
       </c>
-      <c r="G308" s="52">
+      <c r="G308" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F308,Table2[Revenue])</f>
         <v>1510</v>
       </c>
     </row>
     <row r="309" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F309" s="50" t="str">
+      <c r="F309" s="34" t="str">
         <v>Zara Devi</v>
       </c>
-      <c r="G309" s="52">
+      <c r="G309" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F309,Table2[Revenue])</f>
         <v>460</v>
       </c>
     </row>
     <row r="310" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F310" s="50" t="str">
+      <c r="F310" s="34" t="str">
         <v>Arjun Mani</v>
       </c>
-      <c r="G310" s="52">
+      <c r="G310" s="35">
         <f>AVERAGEIF(Table2[Patient Name2],F310,Table2[Revenue])</f>
         <v>870</v>
       </c>
     </row>
     <row r="311" spans="6:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F311" s="53" t="str">
+      <c r="F311" s="36" t="str">
         <v>Bhanu Balan</v>
       </c>
-      <c r="G311" s="55">
+      <c r="G311" s="38">
         <f>AVERAGEIF(Table2[Patient Name2],F311,Table2[Revenue])</f>
         <v>1320</v>
       </c>
@@ -19197,84 +19557,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="40" t="s">
         <v>730</v>
       </c>
-      <c r="B1" s="26"/>
+      <c r="B1" s="40"/>
     </row>
     <row r="2" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="41" t="s">
         <v>731</v>
       </c>
-      <c r="B2" s="29"/>
+      <c r="B2" s="41"/>
     </row>
     <row r="3" spans="1:2" ht="77.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="42" t="s">
         <v>732</v>
       </c>
-      <c r="B3" s="28"/>
+      <c r="B3" s="42"/>
     </row>
     <row r="4" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="41" t="s">
         <v>733</v>
       </c>
-      <c r="B4" s="29"/>
+      <c r="B4" s="41"/>
     </row>
     <row r="5" spans="1:2" ht="77.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="42" t="s">
         <v>770</v>
       </c>
-      <c r="B5" s="28"/>
+      <c r="B5" s="42"/>
     </row>
     <row r="6" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="41" t="s">
         <v>734</v>
       </c>
-      <c r="B6" s="29"/>
+      <c r="B6" s="41"/>
     </row>
     <row r="7" spans="1:2" ht="90.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="42" t="s">
         <v>775</v>
       </c>
-      <c r="B7" s="28"/>
+      <c r="B7" s="42"/>
     </row>
     <row r="8" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="41" t="s">
         <v>735</v>
       </c>
-      <c r="B8" s="29"/>
+      <c r="B8" s="41"/>
     </row>
     <row r="9" spans="1:2" ht="98.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="42" t="s">
         <v>771</v>
       </c>
-      <c r="B9" s="28"/>
+      <c r="B9" s="42"/>
     </row>
     <row r="10" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="41" t="s">
         <v>736</v>
       </c>
-      <c r="B10" s="29"/>
+      <c r="B10" s="41"/>
     </row>
     <row r="11" spans="1:2" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="42" t="s">
         <v>737</v>
       </c>
-      <c r="B11" s="28"/>
+      <c r="B11" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -19291,109 +19651,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="40" t="s">
         <v>738</v>
       </c>
-      <c r="B1" s="26"/>
+      <c r="B1" s="40"/>
     </row>
     <row r="2" spans="1:2" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="43" t="s">
         <v>739</v>
       </c>
-      <c r="B2" s="33"/>
+      <c r="B2" s="43"/>
     </row>
     <row r="3" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="44" t="s">
         <v>740</v>
       </c>
-      <c r="B3" s="31"/>
+      <c r="B3" s="44"/>
     </row>
     <row r="4" spans="1:2" ht="220.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="42" t="s">
         <v>741</v>
       </c>
-      <c r="B4" s="28"/>
+      <c r="B4" s="42"/>
     </row>
     <row r="5" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
-      <c r="B5" s="30"/>
+      <c r="A5" s="45"/>
+      <c r="B5" s="45"/>
     </row>
     <row r="6" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="44" t="s">
         <v>742</v>
       </c>
-      <c r="B6" s="31"/>
+      <c r="B6" s="44"/>
     </row>
     <row r="7" spans="1:2" ht="162" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="46" t="s">
         <v>743</v>
       </c>
-      <c r="B7" s="32"/>
+      <c r="B7" s="46"/>
     </row>
     <row r="8" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="30"/>
-      <c r="B8" s="30"/>
+      <c r="A8" s="45"/>
+      <c r="B8" s="45"/>
     </row>
     <row r="9" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="44" t="s">
         <v>744</v>
       </c>
-      <c r="B9" s="31"/>
+      <c r="B9" s="44"/>
     </row>
     <row r="10" spans="1:2" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="42" t="s">
         <v>745</v>
       </c>
-      <c r="B10" s="28"/>
+      <c r="B10" s="42"/>
     </row>
     <row r="11" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30"/>
+      <c r="A11" s="45"/>
+      <c r="B11" s="45"/>
     </row>
     <row r="12" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="44" t="s">
         <v>746</v>
       </c>
-      <c r="B12" s="31"/>
+      <c r="B12" s="44"/>
     </row>
     <row r="13" spans="1:2" ht="147.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="46" t="s">
         <v>747</v>
       </c>
-      <c r="B13" s="32"/>
+      <c r="B13" s="46"/>
     </row>
     <row r="14" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="30"/>
-      <c r="B14" s="30"/>
+      <c r="A14" s="45"/>
+      <c r="B14" s="45"/>
     </row>
     <row r="15" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="44" t="s">
         <v>748</v>
       </c>
-      <c r="B15" s="31"/>
+      <c r="B15" s="44"/>
     </row>
     <row r="16" spans="1:2" ht="192" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="42" t="s">
         <v>749</v>
       </c>
-      <c r="B16" s="28"/>
+      <c r="B16" s="42"/>
     </row>
     <row r="17" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="30"/>
-      <c r="B17" s="30"/>
+      <c r="A17" s="45"/>
+      <c r="B17" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A11:B11"/>
@@ -19401,6 +19751,16 @@
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -19417,109 +19777,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="47" t="s">
         <v>750</v>
       </c>
-      <c r="B1" s="35"/>
+      <c r="B1" s="47"/>
     </row>
     <row r="2" spans="1:2" ht="45.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="43" t="s">
         <v>739</v>
       </c>
-      <c r="B2" s="33"/>
+      <c r="B2" s="43"/>
     </row>
     <row r="3" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="48" t="s">
         <v>740</v>
       </c>
-      <c r="B3" s="34"/>
+      <c r="B3" s="48"/>
     </row>
     <row r="4" spans="1:2" ht="220.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="42" t="s">
         <v>741</v>
       </c>
-      <c r="B4" s="28"/>
+      <c r="B4" s="42"/>
     </row>
     <row r="5" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
-      <c r="B5" s="30"/>
+      <c r="A5" s="45"/>
+      <c r="B5" s="45"/>
     </row>
     <row r="6" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="48" t="s">
         <v>742</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="48"/>
     </row>
     <row r="7" spans="1:2" ht="162" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="46" t="s">
         <v>743</v>
       </c>
-      <c r="B7" s="32"/>
+      <c r="B7" s="46"/>
     </row>
     <row r="8" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="30"/>
-      <c r="B8" s="30"/>
+      <c r="A8" s="45"/>
+      <c r="B8" s="45"/>
     </row>
     <row r="9" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="48" t="s">
         <v>744</v>
       </c>
-      <c r="B9" s="34"/>
+      <c r="B9" s="48"/>
     </row>
     <row r="10" spans="1:2" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="42" t="s">
         <v>745</v>
       </c>
-      <c r="B10" s="28"/>
+      <c r="B10" s="42"/>
     </row>
     <row r="11" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30"/>
+      <c r="A11" s="45"/>
+      <c r="B11" s="45"/>
     </row>
     <row r="12" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="48" t="s">
         <v>751</v>
       </c>
-      <c r="B12" s="34"/>
+      <c r="B12" s="48"/>
     </row>
     <row r="13" spans="1:2" ht="235.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="46" t="s">
         <v>752</v>
       </c>
-      <c r="B13" s="32"/>
+      <c r="B13" s="46"/>
     </row>
     <row r="14" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="30"/>
-      <c r="B14" s="30"/>
+      <c r="A14" s="45"/>
+      <c r="B14" s="45"/>
     </row>
     <row r="15" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="48" t="s">
         <v>753</v>
       </c>
-      <c r="B15" s="34"/>
+      <c r="B15" s="48"/>
     </row>
     <row r="16" spans="1:2" ht="168.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="42" t="s">
         <v>754</v>
       </c>
-      <c r="B16" s="28"/>
+      <c r="B16" s="42"/>
     </row>
     <row r="17" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="30"/>
-      <c r="B17" s="30"/>
+      <c r="A17" s="45"/>
+      <c r="B17" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A11:B11"/>
@@ -19527,6 +19877,16 @@
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -19543,109 +19903,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="49" t="s">
         <v>755</v>
       </c>
-      <c r="B1" s="37"/>
+      <c r="B1" s="49"/>
     </row>
     <row r="2" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="43" t="s">
         <v>739</v>
       </c>
-      <c r="B2" s="33"/>
+      <c r="B2" s="43"/>
     </row>
     <row r="3" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="50" t="s">
         <v>740</v>
       </c>
-      <c r="B3" s="36"/>
+      <c r="B3" s="50"/>
     </row>
     <row r="4" spans="1:2" ht="220.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="42" t="s">
         <v>741</v>
       </c>
-      <c r="B4" s="28"/>
+      <c r="B4" s="42"/>
     </row>
     <row r="5" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
-      <c r="B5" s="30"/>
+      <c r="A5" s="45"/>
+      <c r="B5" s="45"/>
     </row>
     <row r="6" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="50" t="s">
         <v>742</v>
       </c>
-      <c r="B6" s="36"/>
+      <c r="B6" s="50"/>
     </row>
     <row r="7" spans="1:2" ht="162" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="46" t="s">
         <v>743</v>
       </c>
-      <c r="B7" s="32"/>
+      <c r="B7" s="46"/>
     </row>
     <row r="8" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="30"/>
-      <c r="B8" s="30"/>
+      <c r="A8" s="45"/>
+      <c r="B8" s="45"/>
     </row>
     <row r="9" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="50" t="s">
         <v>744</v>
       </c>
-      <c r="B9" s="36"/>
+      <c r="B9" s="50"/>
     </row>
     <row r="10" spans="1:2" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="42" t="s">
         <v>745</v>
       </c>
-      <c r="B10" s="28"/>
+      <c r="B10" s="42"/>
     </row>
     <row r="11" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30"/>
+      <c r="A11" s="45"/>
+      <c r="B11" s="45"/>
     </row>
     <row r="12" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="50" t="s">
         <v>756</v>
       </c>
-      <c r="B12" s="36"/>
+      <c r="B12" s="50"/>
     </row>
     <row r="13" spans="1:2" ht="183.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="46" t="s">
         <v>757</v>
       </c>
-      <c r="B13" s="32"/>
+      <c r="B13" s="46"/>
     </row>
     <row r="14" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="30"/>
-      <c r="B14" s="30"/>
+      <c r="A14" s="45"/>
+      <c r="B14" s="45"/>
     </row>
     <row r="15" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="50" t="s">
         <v>758</v>
       </c>
-      <c r="B15" s="36"/>
+      <c r="B15" s="50"/>
     </row>
     <row r="16" spans="1:2" ht="159" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="42" t="s">
         <v>759</v>
       </c>
-      <c r="B16" s="28"/>
+      <c r="B16" s="42"/>
     </row>
     <row r="17" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="30"/>
-      <c r="B17" s="30"/>
+      <c r="A17" s="45"/>
+      <c r="B17" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A11:B11"/>
@@ -19653,6 +20003,16 @@
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -19669,109 +20029,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="51" t="s">
         <v>760</v>
       </c>
-      <c r="B1" s="39"/>
+      <c r="B1" s="51"/>
     </row>
     <row r="2" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="43" t="s">
         <v>739</v>
       </c>
-      <c r="B2" s="33"/>
+      <c r="B2" s="43"/>
     </row>
     <row r="3" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="52" t="s">
         <v>740</v>
       </c>
-      <c r="B3" s="38"/>
+      <c r="B3" s="52"/>
     </row>
     <row r="4" spans="1:2" ht="220.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="42" t="s">
         <v>741</v>
       </c>
-      <c r="B4" s="28"/>
+      <c r="B4" s="42"/>
     </row>
     <row r="5" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
-      <c r="B5" s="30"/>
+      <c r="A5" s="45"/>
+      <c r="B5" s="45"/>
     </row>
     <row r="6" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="52" t="s">
         <v>742</v>
       </c>
-      <c r="B6" s="38"/>
+      <c r="B6" s="52"/>
     </row>
     <row r="7" spans="1:2" ht="162" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="46" t="s">
         <v>743</v>
       </c>
-      <c r="B7" s="32"/>
+      <c r="B7" s="46"/>
     </row>
     <row r="8" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="30"/>
-      <c r="B8" s="30"/>
+      <c r="A8" s="45"/>
+      <c r="B8" s="45"/>
     </row>
     <row r="9" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="52" t="s">
         <v>744</v>
       </c>
-      <c r="B9" s="38"/>
+      <c r="B9" s="52"/>
     </row>
     <row r="10" spans="1:2" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="42" t="s">
         <v>745</v>
       </c>
-      <c r="B10" s="28"/>
+      <c r="B10" s="42"/>
     </row>
     <row r="11" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30"/>
+      <c r="A11" s="45"/>
+      <c r="B11" s="45"/>
     </row>
     <row r="12" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="52" t="s">
         <v>761</v>
       </c>
-      <c r="B12" s="38"/>
+      <c r="B12" s="52"/>
     </row>
     <row r="13" spans="1:2" ht="231.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="46" t="s">
         <v>762</v>
       </c>
-      <c r="B13" s="32"/>
+      <c r="B13" s="46"/>
     </row>
     <row r="14" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="30"/>
-      <c r="B14" s="30"/>
+      <c r="A14" s="45"/>
+      <c r="B14" s="45"/>
     </row>
     <row r="15" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="38" t="s">
+      <c r="A15" s="52" t="s">
         <v>763</v>
       </c>
-      <c r="B15" s="38"/>
+      <c r="B15" s="52"/>
     </row>
     <row r="16" spans="1:2" ht="187.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="42" t="s">
         <v>764</v>
       </c>
-      <c r="B16" s="28"/>
+      <c r="B16" s="42"/>
     </row>
     <row r="17" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="30"/>
-      <c r="B17" s="30"/>
+      <c r="A17" s="45"/>
+      <c r="B17" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A11:B11"/>
@@ -19779,6 +20129,16 @@
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -19795,109 +20155,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="53" t="s">
         <v>765</v>
       </c>
-      <c r="B1" s="41"/>
+      <c r="B1" s="53"/>
     </row>
     <row r="2" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="43" t="s">
         <v>739</v>
       </c>
-      <c r="B2" s="33"/>
+      <c r="B2" s="43"/>
     </row>
     <row r="3" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="54" t="s">
         <v>740</v>
       </c>
-      <c r="B3" s="40"/>
+      <c r="B3" s="54"/>
     </row>
     <row r="4" spans="1:2" ht="220.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="42" t="s">
         <v>741</v>
       </c>
-      <c r="B4" s="28"/>
+      <c r="B4" s="42"/>
     </row>
     <row r="5" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
-      <c r="B5" s="30"/>
+      <c r="A5" s="45"/>
+      <c r="B5" s="45"/>
     </row>
     <row r="6" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="54" t="s">
         <v>742</v>
       </c>
-      <c r="B6" s="40"/>
+      <c r="B6" s="54"/>
     </row>
     <row r="7" spans="1:2" ht="162" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="46" t="s">
         <v>743</v>
       </c>
-      <c r="B7" s="32"/>
+      <c r="B7" s="46"/>
     </row>
     <row r="8" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="30"/>
-      <c r="B8" s="30"/>
+      <c r="A8" s="45"/>
+      <c r="B8" s="45"/>
     </row>
     <row r="9" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="54" t="s">
         <v>744</v>
       </c>
-      <c r="B9" s="40"/>
+      <c r="B9" s="54"/>
     </row>
     <row r="10" spans="1:2" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="42" t="s">
         <v>745</v>
       </c>
-      <c r="B10" s="28"/>
+      <c r="B10" s="42"/>
     </row>
     <row r="11" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30"/>
+      <c r="A11" s="45"/>
+      <c r="B11" s="45"/>
     </row>
     <row r="12" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="54" t="s">
         <v>766</v>
       </c>
-      <c r="B12" s="40"/>
+      <c r="B12" s="54"/>
     </row>
     <row r="13" spans="1:2" ht="189" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="46" t="s">
         <v>767</v>
       </c>
-      <c r="B13" s="32"/>
+      <c r="B13" s="46"/>
     </row>
     <row r="14" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="30"/>
-      <c r="B14" s="30"/>
+      <c r="A14" s="45"/>
+      <c r="B14" s="45"/>
     </row>
     <row r="15" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="54" t="s">
         <v>768</v>
       </c>
-      <c r="B15" s="40"/>
+      <c r="B15" s="54"/>
     </row>
     <row r="16" spans="1:2" ht="187.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="42" t="s">
         <v>769</v>
       </c>
-      <c r="B16" s="28"/>
+      <c r="B16" s="42"/>
     </row>
     <row r="17" spans="1:2" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="30"/>
-      <c r="B17" s="30"/>
+      <c r="A17" s="45"/>
+      <c r="B17" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A11:B11"/>
@@ -19905,6 +20255,16 @@
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -19913,7 +20273,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6451C35E-3ABA-48DA-A613-1A7D45B4F684}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.5703125" style="25" bestFit="1" customWidth="1"/>
@@ -20028,6 +20388,72 @@
       </c>
       <c r="C10" t="s">
         <v>794</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="57" t="s">
+        <v>798</v>
+      </c>
+      <c r="C11" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="57" t="s">
+        <v>798</v>
+      </c>
+      <c r="C12" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="57" t="s">
+        <v>798</v>
+      </c>
+      <c r="C13" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>798</v>
+      </c>
+      <c r="C14" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>798</v>
+      </c>
+      <c r="C15" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>798</v>
+      </c>
+      <c r="C16" t="s">
+        <v>806</v>
       </c>
     </row>
   </sheetData>
@@ -20056,21 +20482,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
     </row>
     <row r="2" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -20112,10 +20538,10 @@
       <c r="M2" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="46" t="s">
+      <c r="N2" s="30" t="s">
         <v>785</v>
       </c>
-      <c r="O2" s="46" t="s">
+      <c r="O2" s="30" t="s">
         <v>795</v>
       </c>
     </row>
@@ -20160,11 +20586,11 @@
       <c r="M3" s="16">
         <v>870</v>
       </c>
-      <c r="N3" s="44">
+      <c r="N3" s="28">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1670</v>
       </c>
-      <c r="O3" s="56">
+      <c r="O3" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -20210,11 +20636,11 @@
       <c r="M4" s="17">
         <v>870</v>
       </c>
-      <c r="N4" s="43">
+      <c r="N4" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1620</v>
       </c>
-      <c r="O4" s="56">
+      <c r="O4" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -20260,11 +20686,11 @@
       <c r="M5" s="16">
         <v>220</v>
       </c>
-      <c r="N5" s="43">
+      <c r="N5" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>720</v>
       </c>
-      <c r="O5" s="56">
+      <c r="O5" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -20310,11 +20736,11 @@
       <c r="M6" s="17">
         <v>230</v>
       </c>
-      <c r="N6" s="43">
+      <c r="N6" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1230</v>
       </c>
-      <c r="O6" s="56">
+      <c r="O6" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -20360,11 +20786,11 @@
       <c r="M7" s="16">
         <v>220</v>
       </c>
-      <c r="N7" s="43">
+      <c r="N7" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>520</v>
       </c>
-      <c r="O7" s="56">
+      <c r="O7" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -20410,11 +20836,11 @@
       <c r="M8" s="17">
         <v>280</v>
       </c>
-      <c r="N8" s="43">
+      <c r="N8" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>980</v>
       </c>
-      <c r="O8" s="56">
+      <c r="O8" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -20460,16 +20886,16 @@
       <c r="M9" s="16">
         <v>210</v>
       </c>
-      <c r="N9" s="43">
+      <c r="N9" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>860</v>
       </c>
-      <c r="O9" s="56">
+      <c r="O9" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
-      <c r="S9" s="27"/>
-      <c r="T9" s="27"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="55"/>
     </row>
     <row r="10" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
@@ -20512,11 +20938,11 @@
       <c r="M10" s="17">
         <v>290</v>
       </c>
-      <c r="N10" s="43">
+      <c r="N10" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>890</v>
       </c>
-      <c r="O10" s="56">
+      <c r="O10" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -20562,11 +20988,11 @@
       <c r="M11" s="16">
         <v>720</v>
       </c>
-      <c r="N11" s="43">
+      <c r="N11" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1670</v>
       </c>
-      <c r="O11" s="56">
+      <c r="O11" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -20612,11 +21038,11 @@
       <c r="M12" s="17">
         <v>190</v>
       </c>
-      <c r="N12" s="43">
+      <c r="N12" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>540</v>
       </c>
-      <c r="O12" s="56">
+      <c r="O12" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -20662,11 +21088,11 @@
       <c r="M13" s="16">
         <v>320</v>
       </c>
-      <c r="N13" s="43">
+      <c r="N13" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1220</v>
       </c>
-      <c r="O13" s="56">
+      <c r="O13" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -20712,11 +21138,11 @@
       <c r="M14" s="17">
         <v>300</v>
       </c>
-      <c r="N14" s="43">
+      <c r="N14" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1200</v>
       </c>
-      <c r="O14" s="56">
+      <c r="O14" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -20762,11 +21188,11 @@
       <c r="M15" s="16">
         <v>380</v>
       </c>
-      <c r="N15" s="43">
+      <c r="N15" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>830</v>
       </c>
-      <c r="O15" s="56">
+      <c r="O15" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -20812,11 +21238,11 @@
       <c r="M16" s="17">
         <v>350</v>
       </c>
-      <c r="N16" s="43">
+      <c r="N16" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>750</v>
       </c>
-      <c r="O16" s="56">
+      <c r="O16" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -20862,11 +21288,11 @@
       <c r="M17" s="16">
         <v>490</v>
       </c>
-      <c r="N17" s="43">
+      <c r="N17" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1140</v>
       </c>
-      <c r="O17" s="56">
+      <c r="O17" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -20912,11 +21338,11 @@
       <c r="M18" s="17">
         <v>500</v>
       </c>
-      <c r="N18" s="43">
+      <c r="N18" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1350</v>
       </c>
-      <c r="O18" s="56">
+      <c r="O18" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -20962,11 +21388,11 @@
       <c r="M19" s="16">
         <v>280</v>
       </c>
-      <c r="N19" s="43">
+      <c r="N19" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>980</v>
       </c>
-      <c r="O19" s="56">
+      <c r="O19" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -21012,11 +21438,11 @@
       <c r="M20" s="17">
         <v>540</v>
       </c>
-      <c r="N20" s="43">
+      <c r="N20" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1190</v>
       </c>
-      <c r="O20" s="56">
+      <c r="O20" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -21062,11 +21488,11 @@
       <c r="M21" s="16">
         <v>380</v>
       </c>
-      <c r="N21" s="43">
+      <c r="N21" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1330</v>
       </c>
-      <c r="O21" s="56">
+      <c r="O21" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -21112,11 +21538,11 @@
       <c r="M22" s="17">
         <v>550</v>
       </c>
-      <c r="N22" s="43">
+      <c r="N22" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1550</v>
       </c>
-      <c r="O22" s="56">
+      <c r="O22" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -21162,11 +21588,11 @@
       <c r="M23" s="16">
         <v>280</v>
       </c>
-      <c r="N23" s="43">
+      <c r="N23" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>930</v>
       </c>
-      <c r="O23" s="56">
+      <c r="O23" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -21212,11 +21638,11 @@
       <c r="M24" s="17">
         <v>350</v>
       </c>
-      <c r="N24" s="43">
+      <c r="N24" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1000</v>
       </c>
-      <c r="O24" s="56">
+      <c r="O24" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -21262,11 +21688,11 @@
       <c r="M25" s="16">
         <v>170</v>
       </c>
-      <c r="N25" s="43">
+      <c r="N25" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>470</v>
       </c>
-      <c r="O25" s="56">
+      <c r="O25" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -21312,11 +21738,11 @@
       <c r="M26" s="17">
         <v>250</v>
       </c>
-      <c r="N26" s="43">
+      <c r="N26" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>650</v>
       </c>
-      <c r="O26" s="56">
+      <c r="O26" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -21362,11 +21788,11 @@
       <c r="M27" s="16">
         <v>150</v>
       </c>
-      <c r="N27" s="43">
+      <c r="N27" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>600</v>
       </c>
-      <c r="O27" s="56">
+      <c r="O27" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -21412,11 +21838,11 @@
       <c r="M28" s="17">
         <v>260</v>
       </c>
-      <c r="N28" s="43">
+      <c r="N28" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1060</v>
       </c>
-      <c r="O28" s="56">
+      <c r="O28" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -21462,11 +21888,11 @@
       <c r="M29" s="16">
         <v>200</v>
       </c>
-      <c r="N29" s="43">
+      <c r="N29" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>550</v>
       </c>
-      <c r="O29" s="56">
+      <c r="O29" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -21512,11 +21938,11 @@
       <c r="M30" s="17">
         <v>570</v>
       </c>
-      <c r="N30" s="43">
+      <c r="N30" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1320</v>
       </c>
-      <c r="O30" s="56">
+      <c r="O30" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -21562,11 +21988,11 @@
       <c r="M31" s="16">
         <v>220</v>
       </c>
-      <c r="N31" s="43">
+      <c r="N31" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>520</v>
       </c>
-      <c r="O31" s="56">
+      <c r="O31" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -21612,11 +22038,11 @@
       <c r="M32" s="17">
         <v>210</v>
       </c>
-      <c r="N32" s="43">
+      <c r="N32" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>960</v>
       </c>
-      <c r="O32" s="56">
+      <c r="O32" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -21662,11 +22088,11 @@
       <c r="M33" s="16">
         <v>260</v>
       </c>
-      <c r="N33" s="43">
+      <c r="N33" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>960</v>
       </c>
-      <c r="O33" s="56">
+      <c r="O33" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -21712,11 +22138,11 @@
       <c r="M34" s="17">
         <v>380</v>
       </c>
-      <c r="N34" s="43">
+      <c r="N34" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1280</v>
       </c>
-      <c r="O34" s="56">
+      <c r="O34" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -21762,11 +22188,11 @@
       <c r="M35" s="16">
         <v>850</v>
       </c>
-      <c r="N35" s="43">
+      <c r="N35" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1600</v>
       </c>
-      <c r="O35" s="56">
+      <c r="O35" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -21812,11 +22238,11 @@
       <c r="M36" s="17">
         <v>170</v>
       </c>
-      <c r="N36" s="43">
+      <c r="N36" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>820</v>
       </c>
-      <c r="O36" s="56">
+      <c r="O36" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -21862,11 +22288,11 @@
       <c r="M37" s="16">
         <v>680</v>
       </c>
-      <c r="N37" s="43">
+      <c r="N37" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1580</v>
       </c>
-      <c r="O37" s="56">
+      <c r="O37" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -21912,11 +22338,11 @@
       <c r="M38" s="17">
         <v>300</v>
       </c>
-      <c r="N38" s="43">
+      <c r="N38" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>700</v>
       </c>
-      <c r="O38" s="56">
+      <c r="O38" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -21962,11 +22388,11 @@
       <c r="M39" s="16">
         <v>490</v>
       </c>
-      <c r="N39" s="43">
+      <c r="N39" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1340</v>
       </c>
-      <c r="O39" s="56">
+      <c r="O39" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -22012,11 +22438,11 @@
       <c r="M40" s="17">
         <v>400</v>
       </c>
-      <c r="N40" s="43">
+      <c r="N40" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1400</v>
       </c>
-      <c r="O40" s="56">
+      <c r="O40" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -22062,11 +22488,11 @@
       <c r="M41" s="16">
         <v>430</v>
       </c>
-      <c r="N41" s="43">
+      <c r="N41" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1130</v>
       </c>
-      <c r="O41" s="56">
+      <c r="O41" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -22112,11 +22538,11 @@
       <c r="M42" s="17">
         <v>260</v>
       </c>
-      <c r="N42" s="43">
+      <c r="N42" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>760</v>
       </c>
-      <c r="O42" s="56">
+      <c r="O42" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -22162,11 +22588,11 @@
       <c r="M43" s="16">
         <v>320</v>
       </c>
-      <c r="N43" s="43">
+      <c r="N43" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>670</v>
       </c>
-      <c r="O43" s="56">
+      <c r="O43" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -22212,11 +22638,11 @@
       <c r="M44" s="17">
         <v>260</v>
       </c>
-      <c r="N44" s="43">
+      <c r="N44" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>660</v>
       </c>
-      <c r="O44" s="56">
+      <c r="O44" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -22262,11 +22688,11 @@
       <c r="M45" s="16">
         <v>340</v>
       </c>
-      <c r="N45" s="43">
+      <c r="N45" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1140</v>
       </c>
-      <c r="O45" s="56">
+      <c r="O45" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -22312,11 +22738,11 @@
       <c r="M46" s="17">
         <v>200</v>
       </c>
-      <c r="N46" s="43">
+      <c r="N46" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>750</v>
       </c>
-      <c r="O46" s="56">
+      <c r="O46" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -22362,11 +22788,11 @@
       <c r="M47" s="16">
         <v>140</v>
       </c>
-      <c r="N47" s="43">
+      <c r="N47" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>690</v>
       </c>
-      <c r="O47" s="56">
+      <c r="O47" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -22412,11 +22838,11 @@
       <c r="M48" s="17">
         <v>350</v>
       </c>
-      <c r="N48" s="43">
+      <c r="N48" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>850</v>
       </c>
-      <c r="O48" s="56">
+      <c r="O48" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -22462,11 +22888,11 @@
       <c r="M49" s="16">
         <v>180</v>
       </c>
-      <c r="N49" s="43">
+      <c r="N49" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>630</v>
       </c>
-      <c r="O49" s="56">
+      <c r="O49" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -22512,11 +22938,11 @@
       <c r="M50" s="17">
         <v>260</v>
       </c>
-      <c r="N50" s="43">
+      <c r="N50" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>760</v>
       </c>
-      <c r="O50" s="56">
+      <c r="O50" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -22562,11 +22988,11 @@
       <c r="M51" s="16">
         <v>360</v>
       </c>
-      <c r="N51" s="43">
+      <c r="N51" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1160</v>
       </c>
-      <c r="O51" s="56">
+      <c r="O51" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -22612,11 +23038,11 @@
       <c r="M52" s="17">
         <v>740</v>
       </c>
-      <c r="N52" s="43">
+      <c r="N52" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1790</v>
       </c>
-      <c r="O52" s="56">
+      <c r="O52" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -22662,11 +23088,11 @@
       <c r="M53" s="16">
         <v>220</v>
       </c>
-      <c r="N53" s="43">
+      <c r="N53" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1070</v>
       </c>
-      <c r="O53" s="56">
+      <c r="O53" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -22712,11 +23138,11 @@
       <c r="M54" s="17">
         <v>600</v>
       </c>
-      <c r="N54" s="43">
+      <c r="N54" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1450</v>
       </c>
-      <c r="O54" s="56">
+      <c r="O54" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -22762,11 +23188,11 @@
       <c r="M55" s="16">
         <v>420</v>
       </c>
-      <c r="N55" s="43">
+      <c r="N55" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1170</v>
       </c>
-      <c r="O55" s="56">
+      <c r="O55" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -22812,11 +23238,11 @@
       <c r="M56" s="17">
         <v>110</v>
       </c>
-      <c r="N56" s="43">
+      <c r="N56" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>460</v>
       </c>
-      <c r="O56" s="56">
+      <c r="O56" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -22862,11 +23288,11 @@
       <c r="M57" s="16">
         <v>340</v>
       </c>
-      <c r="N57" s="43">
+      <c r="N57" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>690</v>
       </c>
-      <c r="O57" s="56">
+      <c r="O57" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -22912,11 +23338,11 @@
       <c r="M58" s="17">
         <v>300</v>
       </c>
-      <c r="N58" s="43">
+      <c r="N58" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>650</v>
       </c>
-      <c r="O58" s="56">
+      <c r="O58" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -22962,11 +23388,11 @@
       <c r="M59" s="16">
         <v>440</v>
       </c>
-      <c r="N59" s="43">
+      <c r="N59" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1040</v>
       </c>
-      <c r="O59" s="56">
+      <c r="O59" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -23012,11 +23438,11 @@
       <c r="M60" s="17">
         <v>170</v>
       </c>
-      <c r="N60" s="43">
+      <c r="N60" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>770</v>
       </c>
-      <c r="O60" s="56">
+      <c r="O60" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -23062,11 +23488,11 @@
       <c r="M61" s="16">
         <v>140</v>
       </c>
-      <c r="N61" s="43">
+      <c r="N61" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>590</v>
       </c>
-      <c r="O61" s="56">
+      <c r="O61" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -23112,11 +23538,11 @@
       <c r="M62" s="17">
         <v>440</v>
       </c>
-      <c r="N62" s="43">
+      <c r="N62" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1590</v>
       </c>
-      <c r="O62" s="56">
+      <c r="O62" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -23162,11 +23588,11 @@
       <c r="M63" s="16">
         <v>480</v>
       </c>
-      <c r="N63" s="43">
+      <c r="N63" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1430</v>
       </c>
-      <c r="O63" s="56">
+      <c r="O63" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -23212,11 +23638,11 @@
       <c r="M64" s="17">
         <v>660</v>
       </c>
-      <c r="N64" s="43">
+      <c r="N64" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1710</v>
       </c>
-      <c r="O64" s="56">
+      <c r="O64" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -23262,11 +23688,11 @@
       <c r="M65" s="16">
         <v>240</v>
       </c>
-      <c r="N65" s="43">
+      <c r="N65" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>640</v>
       </c>
-      <c r="O65" s="56">
+      <c r="O65" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -23312,11 +23738,11 @@
       <c r="M66" s="17">
         <v>380</v>
       </c>
-      <c r="N66" s="43">
+      <c r="N66" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1130</v>
       </c>
-      <c r="O66" s="56">
+      <c r="O66" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -23362,11 +23788,11 @@
       <c r="M67" s="16">
         <v>200</v>
       </c>
-      <c r="N67" s="43">
+      <c r="N67" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>600</v>
       </c>
-      <c r="O67" s="56">
+      <c r="O67" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -23412,11 +23838,11 @@
       <c r="M68" s="17">
         <v>240</v>
       </c>
-      <c r="N68" s="43">
+      <c r="N68" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>790</v>
       </c>
-      <c r="O68" s="56">
+      <c r="O68" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -23462,11 +23888,11 @@
       <c r="M69" s="16">
         <v>350</v>
       </c>
-      <c r="N69" s="43">
+      <c r="N69" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1100</v>
       </c>
-      <c r="O69" s="56">
+      <c r="O69" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -23512,11 +23938,11 @@
       <c r="M70" s="17">
         <v>340</v>
       </c>
-      <c r="N70" s="43">
+      <c r="N70" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1340</v>
       </c>
-      <c r="O70" s="56">
+      <c r="O70" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -23562,11 +23988,11 @@
       <c r="M71" s="16">
         <v>520</v>
       </c>
-      <c r="N71" s="43">
+      <c r="N71" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1620</v>
       </c>
-      <c r="O71" s="56">
+      <c r="O71" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -23612,11 +24038,11 @@
       <c r="M72" s="17">
         <v>550</v>
       </c>
-      <c r="N72" s="43">
+      <c r="N72" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1300</v>
       </c>
-      <c r="O72" s="56">
+      <c r="O72" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -23662,11 +24088,11 @@
       <c r="M73" s="16">
         <v>170</v>
       </c>
-      <c r="N73" s="43">
+      <c r="N73" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>570</v>
       </c>
-      <c r="O73" s="56">
+      <c r="O73" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -23712,11 +24138,11 @@
       <c r="M74" s="17">
         <v>170</v>
       </c>
-      <c r="N74" s="43">
+      <c r="N74" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>520</v>
       </c>
-      <c r="O74" s="56">
+      <c r="O74" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -23762,11 +24188,11 @@
       <c r="M75" s="16">
         <v>400</v>
       </c>
-      <c r="N75" s="43">
+      <c r="N75" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1150</v>
       </c>
-      <c r="O75" s="56">
+      <c r="O75" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -23812,11 +24238,11 @@
       <c r="M76" s="17">
         <v>350</v>
       </c>
-      <c r="N76" s="43">
+      <c r="N76" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>850</v>
       </c>
-      <c r="O76" s="56">
+      <c r="O76" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -23862,11 +24288,11 @@
       <c r="M77" s="16">
         <v>500</v>
       </c>
-      <c r="N77" s="43">
+      <c r="N77" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1350</v>
       </c>
-      <c r="O77" s="56">
+      <c r="O77" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -23912,11 +24338,11 @@
       <c r="M78" s="17">
         <v>330</v>
       </c>
-      <c r="N78" s="43">
+      <c r="N78" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1180</v>
       </c>
-      <c r="O78" s="56">
+      <c r="O78" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -23962,11 +24388,11 @@
       <c r="M79" s="16">
         <v>170</v>
       </c>
-      <c r="N79" s="43">
+      <c r="N79" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>470</v>
       </c>
-      <c r="O79" s="56">
+      <c r="O79" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -24012,11 +24438,11 @@
       <c r="M80" s="17">
         <v>360</v>
       </c>
-      <c r="N80" s="43">
+      <c r="N80" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1160</v>
       </c>
-      <c r="O80" s="56">
+      <c r="O80" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -24062,11 +24488,11 @@
       <c r="M81" s="16">
         <v>650</v>
       </c>
-      <c r="N81" s="43">
+      <c r="N81" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1450</v>
       </c>
-      <c r="O81" s="56">
+      <c r="O81" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -24112,11 +24538,11 @@
       <c r="M82" s="17">
         <v>200</v>
       </c>
-      <c r="N82" s="43">
+      <c r="N82" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>900</v>
       </c>
-      <c r="O82" s="56">
+      <c r="O82" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -24162,11 +24588,11 @@
       <c r="M83" s="16">
         <v>190</v>
       </c>
-      <c r="N83" s="43">
+      <c r="N83" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>590</v>
       </c>
-      <c r="O83" s="56">
+      <c r="O83" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -24212,11 +24638,11 @@
       <c r="M84" s="17">
         <v>350</v>
       </c>
-      <c r="N84" s="43">
+      <c r="N84" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>850</v>
       </c>
-      <c r="O84" s="56">
+      <c r="O84" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -24262,11 +24688,11 @@
       <c r="M85" s="16">
         <v>630</v>
       </c>
-      <c r="N85" s="43">
+      <c r="N85" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1530</v>
       </c>
-      <c r="O85" s="56">
+      <c r="O85" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -24312,11 +24738,11 @@
       <c r="M86" s="17">
         <v>470</v>
       </c>
-      <c r="N86" s="43">
+      <c r="N86" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1020</v>
       </c>
-      <c r="O86" s="56">
+      <c r="O86" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -24362,11 +24788,11 @@
       <c r="M87" s="16">
         <v>310</v>
       </c>
-      <c r="N87" s="43">
+      <c r="N87" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>760</v>
       </c>
-      <c r="O87" s="56">
+      <c r="O87" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -24412,11 +24838,11 @@
       <c r="M88" s="17">
         <v>280</v>
       </c>
-      <c r="N88" s="43">
+      <c r="N88" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>730</v>
       </c>
-      <c r="O88" s="56">
+      <c r="O88" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -24462,11 +24888,11 @@
       <c r="M89" s="16">
         <v>620</v>
       </c>
-      <c r="N89" s="43">
+      <c r="N89" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1770</v>
       </c>
-      <c r="O89" s="56">
+      <c r="O89" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -24512,11 +24938,11 @@
       <c r="M90" s="17">
         <v>900</v>
       </c>
-      <c r="N90" s="43">
+      <c r="N90" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1650</v>
       </c>
-      <c r="O90" s="56">
+      <c r="O90" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -24562,11 +24988,11 @@
       <c r="M91" s="16">
         <v>340</v>
       </c>
-      <c r="N91" s="43">
+      <c r="N91" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1190</v>
       </c>
-      <c r="O91" s="56">
+      <c r="O91" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -24612,11 +25038,11 @@
       <c r="M92" s="17">
         <v>340</v>
       </c>
-      <c r="N92" s="43">
+      <c r="N92" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>690</v>
       </c>
-      <c r="O92" s="56">
+      <c r="O92" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -24662,11 +25088,11 @@
       <c r="M93" s="16">
         <v>350</v>
       </c>
-      <c r="N93" s="43">
+      <c r="N93" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>950</v>
       </c>
-      <c r="O93" s="56">
+      <c r="O93" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -24712,11 +25138,11 @@
       <c r="M94" s="17">
         <v>620</v>
       </c>
-      <c r="N94" s="43">
+      <c r="N94" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1620</v>
       </c>
-      <c r="O94" s="56">
+      <c r="O94" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -24762,11 +25188,11 @@
       <c r="M95" s="16">
         <v>100</v>
       </c>
-      <c r="N95" s="43">
+      <c r="N95" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>550</v>
       </c>
-      <c r="O95" s="56">
+      <c r="O95" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -24812,11 +25238,11 @@
       <c r="M96" s="17">
         <v>260</v>
       </c>
-      <c r="N96" s="43">
+      <c r="N96" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1260</v>
       </c>
-      <c r="O96" s="56">
+      <c r="O96" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -24862,11 +25288,11 @@
       <c r="M97" s="16">
         <v>250</v>
       </c>
-      <c r="N97" s="43">
+      <c r="N97" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>550</v>
       </c>
-      <c r="O97" s="56">
+      <c r="O97" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -24912,11 +25338,11 @@
       <c r="M98" s="17">
         <v>400</v>
       </c>
-      <c r="N98" s="43">
+      <c r="N98" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1450</v>
       </c>
-      <c r="O98" s="56">
+      <c r="O98" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -24962,11 +25388,11 @@
       <c r="M99" s="16">
         <v>580</v>
       </c>
-      <c r="N99" s="43">
+      <c r="N99" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1580</v>
       </c>
-      <c r="O99" s="56">
+      <c r="O99" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -25012,11 +25438,11 @@
       <c r="M100" s="17">
         <v>260</v>
       </c>
-      <c r="N100" s="43">
+      <c r="N100" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1010</v>
       </c>
-      <c r="O100" s="56">
+      <c r="O100" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -25062,11 +25488,11 @@
       <c r="M101" s="16">
         <v>350</v>
       </c>
-      <c r="N101" s="43">
+      <c r="N101" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1550</v>
       </c>
-      <c r="O101" s="56">
+      <c r="O101" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -25112,11 +25538,11 @@
       <c r="M102" s="17">
         <v>400</v>
       </c>
-      <c r="N102" s="43">
+      <c r="N102" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>800</v>
       </c>
-      <c r="O102" s="56">
+      <c r="O102" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -25162,11 +25588,11 @@
       <c r="M103" s="16">
         <v>190</v>
       </c>
-      <c r="N103" s="43">
+      <c r="N103" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>790</v>
       </c>
-      <c r="O103" s="56">
+      <c r="O103" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -25212,11 +25638,11 @@
       <c r="M104" s="17">
         <v>90</v>
       </c>
-      <c r="N104" s="43">
+      <c r="N104" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>640</v>
       </c>
-      <c r="O104" s="56">
+      <c r="O104" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -25262,11 +25688,11 @@
       <c r="M105" s="16">
         <v>450</v>
       </c>
-      <c r="N105" s="43">
+      <c r="N105" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1200</v>
       </c>
-      <c r="O105" s="56">
+      <c r="O105" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -25312,11 +25738,11 @@
       <c r="M106" s="17">
         <v>140</v>
       </c>
-      <c r="N106" s="43">
+      <c r="N106" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>790</v>
       </c>
-      <c r="O106" s="56">
+      <c r="O106" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -25362,11 +25788,11 @@
       <c r="M107" s="16">
         <v>300</v>
       </c>
-      <c r="N107" s="43">
+      <c r="N107" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1050</v>
       </c>
-      <c r="O107" s="56">
+      <c r="O107" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -25412,11 +25838,11 @@
       <c r="M108" s="17">
         <v>330</v>
       </c>
-      <c r="N108" s="43">
+      <c r="N108" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>680</v>
       </c>
-      <c r="O108" s="56">
+      <c r="O108" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -25462,11 +25888,11 @@
       <c r="M109" s="16">
         <v>900</v>
       </c>
-      <c r="N109" s="43">
+      <c r="N109" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1850</v>
       </c>
-      <c r="O109" s="56">
+      <c r="O109" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -25512,11 +25938,11 @@
       <c r="M110" s="17">
         <v>330</v>
       </c>
-      <c r="N110" s="43">
+      <c r="N110" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1280</v>
       </c>
-      <c r="O110" s="56">
+      <c r="O110" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -25562,11 +25988,11 @@
       <c r="M111" s="16">
         <v>470</v>
       </c>
-      <c r="N111" s="43">
+      <c r="N111" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1320</v>
       </c>
-      <c r="O111" s="56">
+      <c r="O111" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -25612,11 +26038,11 @@
       <c r="M112" s="17">
         <v>420</v>
       </c>
-      <c r="N112" s="43">
+      <c r="N112" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1270</v>
       </c>
-      <c r="O112" s="56">
+      <c r="O112" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -25662,11 +26088,11 @@
       <c r="M113" s="16">
         <v>890</v>
       </c>
-      <c r="N113" s="43">
+      <c r="N113" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1640</v>
       </c>
-      <c r="O113" s="56">
+      <c r="O113" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -25712,11 +26138,11 @@
       <c r="M114" s="17">
         <v>370</v>
       </c>
-      <c r="N114" s="43">
+      <c r="N114" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1270</v>
       </c>
-      <c r="O114" s="56">
+      <c r="O114" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -25762,11 +26188,11 @@
       <c r="M115" s="16">
         <v>540</v>
       </c>
-      <c r="N115" s="43">
+      <c r="N115" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1440</v>
       </c>
-      <c r="O115" s="56">
+      <c r="O115" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -25812,11 +26238,11 @@
       <c r="M116" s="17">
         <v>500</v>
       </c>
-      <c r="N116" s="43">
+      <c r="N116" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1150</v>
       </c>
-      <c r="O116" s="56">
+      <c r="O116" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -25862,11 +26288,11 @@
       <c r="M117" s="16">
         <v>310</v>
       </c>
-      <c r="N117" s="43">
+      <c r="N117" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1160</v>
       </c>
-      <c r="O117" s="56">
+      <c r="O117" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -25912,11 +26338,11 @@
       <c r="M118" s="17">
         <v>130</v>
       </c>
-      <c r="N118" s="43">
+      <c r="N118" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>580</v>
       </c>
-      <c r="O118" s="56">
+      <c r="O118" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -25962,11 +26388,11 @@
       <c r="M119" s="16">
         <v>170</v>
       </c>
-      <c r="N119" s="43">
+      <c r="N119" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>620</v>
       </c>
-      <c r="O119" s="56">
+      <c r="O119" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -26012,11 +26438,11 @@
       <c r="M120" s="17">
         <v>240</v>
       </c>
-      <c r="N120" s="43">
+      <c r="N120" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>640</v>
       </c>
-      <c r="O120" s="56">
+      <c r="O120" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -26062,11 +26488,11 @@
       <c r="M121" s="16">
         <v>440</v>
       </c>
-      <c r="N121" s="43">
+      <c r="N121" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1090</v>
       </c>
-      <c r="O121" s="56">
+      <c r="O121" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -26112,11 +26538,11 @@
       <c r="M122" s="17">
         <v>390</v>
       </c>
-      <c r="N122" s="43">
+      <c r="N122" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1090</v>
       </c>
-      <c r="O122" s="56">
+      <c r="O122" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -26162,11 +26588,11 @@
       <c r="M123" s="16">
         <v>200</v>
       </c>
-      <c r="N123" s="43">
+      <c r="N123" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>750</v>
       </c>
-      <c r="O123" s="56">
+      <c r="O123" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -26212,11 +26638,11 @@
       <c r="M124" s="17">
         <v>290</v>
       </c>
-      <c r="N124" s="43">
+      <c r="N124" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>740</v>
       </c>
-      <c r="O124" s="56">
+      <c r="O124" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -26262,11 +26688,11 @@
       <c r="M125" s="16">
         <v>630</v>
       </c>
-      <c r="N125" s="43">
+      <c r="N125" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1430</v>
       </c>
-      <c r="O125" s="56">
+      <c r="O125" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -26312,11 +26738,11 @@
       <c r="M126" s="17">
         <v>310</v>
       </c>
-      <c r="N126" s="43">
+      <c r="N126" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1060</v>
       </c>
-      <c r="O126" s="56">
+      <c r="O126" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -26362,11 +26788,11 @@
       <c r="M127" s="16">
         <v>490</v>
       </c>
-      <c r="N127" s="43">
+      <c r="N127" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1390</v>
       </c>
-      <c r="O127" s="56">
+      <c r="O127" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -26412,11 +26838,11 @@
       <c r="M128" s="17">
         <v>730</v>
       </c>
-      <c r="N128" s="43">
+      <c r="N128" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1680</v>
       </c>
-      <c r="O128" s="56">
+      <c r="O128" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -26462,11 +26888,11 @@
       <c r="M129" s="16">
         <v>550</v>
       </c>
-      <c r="N129" s="43">
+      <c r="N129" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1550</v>
       </c>
-      <c r="O129" s="56">
+      <c r="O129" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -26512,11 +26938,11 @@
       <c r="M130" s="17">
         <v>160</v>
       </c>
-      <c r="N130" s="43">
+      <c r="N130" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>510</v>
       </c>
-      <c r="O130" s="56">
+      <c r="O130" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -26562,11 +26988,11 @@
       <c r="M131" s="16">
         <v>480</v>
       </c>
-      <c r="N131" s="43">
+      <c r="N131" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1630</v>
       </c>
-      <c r="O131" s="56">
+      <c r="O131" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -26612,11 +27038,11 @@
       <c r="M132" s="17">
         <v>410</v>
       </c>
-      <c r="N132" s="43">
+      <c r="N132" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1310</v>
       </c>
-      <c r="O132" s="56">
+      <c r="O132" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -26662,11 +27088,11 @@
       <c r="M133" s="16">
         <v>360</v>
       </c>
-      <c r="N133" s="43">
+      <c r="N133" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1510</v>
       </c>
-      <c r="O133" s="56">
+      <c r="O133" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -26712,11 +27138,11 @@
       <c r="M134" s="17">
         <v>530</v>
       </c>
-      <c r="N134" s="43">
+      <c r="N134" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1330</v>
       </c>
-      <c r="O134" s="56">
+      <c r="O134" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -26762,11 +27188,11 @@
       <c r="M135" s="16">
         <v>750</v>
       </c>
-      <c r="N135" s="43">
+      <c r="N135" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1550</v>
       </c>
-      <c r="O135" s="56">
+      <c r="O135" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -26812,11 +27238,11 @@
       <c r="M136" s="17">
         <v>270</v>
       </c>
-      <c r="N136" s="43">
+      <c r="N136" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>670</v>
       </c>
-      <c r="O136" s="56">
+      <c r="O136" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -26862,11 +27288,11 @@
       <c r="M137" s="16">
         <v>410</v>
       </c>
-      <c r="N137" s="43">
+      <c r="N137" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1110</v>
       </c>
-      <c r="O137" s="56">
+      <c r="O137" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -26912,11 +27338,11 @@
       <c r="M138" s="17">
         <v>880</v>
       </c>
-      <c r="N138" s="43">
+      <c r="N138" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1580</v>
       </c>
-      <c r="O138" s="56">
+      <c r="O138" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -26962,11 +27388,11 @@
       <c r="M139" s="16">
         <v>240</v>
       </c>
-      <c r="N139" s="43">
+      <c r="N139" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>590</v>
       </c>
-      <c r="O139" s="56">
+      <c r="O139" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -27012,11 +27438,11 @@
       <c r="M140" s="17">
         <v>650</v>
       </c>
-      <c r="N140" s="43">
+      <c r="N140" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1800</v>
       </c>
-      <c r="O140" s="56">
+      <c r="O140" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -27062,11 +27488,11 @@
       <c r="M141" s="16">
         <v>100</v>
       </c>
-      <c r="N141" s="43">
+      <c r="N141" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>550</v>
       </c>
-      <c r="O141" s="56">
+      <c r="O141" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -27112,11 +27538,11 @@
       <c r="M142" s="17">
         <v>270</v>
       </c>
-      <c r="N142" s="43">
+      <c r="N142" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>970</v>
       </c>
-      <c r="O142" s="56">
+      <c r="O142" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -27162,11 +27588,11 @@
       <c r="M143" s="16">
         <v>260</v>
       </c>
-      <c r="N143" s="43">
+      <c r="N143" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1110</v>
       </c>
-      <c r="O143" s="56">
+      <c r="O143" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -27212,11 +27638,11 @@
       <c r="M144" s="17">
         <v>210</v>
       </c>
-      <c r="N144" s="43">
+      <c r="N144" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>660</v>
       </c>
-      <c r="O144" s="56">
+      <c r="O144" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -27262,11 +27688,11 @@
       <c r="M145" s="16">
         <v>490</v>
       </c>
-      <c r="N145" s="43">
+      <c r="N145" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1240</v>
       </c>
-      <c r="O145" s="56">
+      <c r="O145" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -27312,11 +27738,11 @@
       <c r="M146" s="17">
         <v>830</v>
       </c>
-      <c r="N146" s="43">
+      <c r="N146" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1530</v>
       </c>
-      <c r="O146" s="56">
+      <c r="O146" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -27362,11 +27788,11 @@
       <c r="M147" s="16">
         <v>530</v>
       </c>
-      <c r="N147" s="43">
+      <c r="N147" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1330</v>
       </c>
-      <c r="O147" s="56">
+      <c r="O147" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -27412,11 +27838,11 @@
       <c r="M148" s="17">
         <v>350</v>
       </c>
-      <c r="N148" s="43">
+      <c r="N148" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1200</v>
       </c>
-      <c r="O148" s="56">
+      <c r="O148" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -27462,11 +27888,11 @@
       <c r="M149" s="16">
         <v>530</v>
       </c>
-      <c r="N149" s="43">
+      <c r="N149" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1680</v>
       </c>
-      <c r="O149" s="56">
+      <c r="O149" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -27512,11 +27938,11 @@
       <c r="M150" s="17">
         <v>360</v>
       </c>
-      <c r="N150" s="43">
+      <c r="N150" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>960</v>
       </c>
-      <c r="O150" s="56">
+      <c r="O150" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -27562,11 +27988,11 @@
       <c r="M151" s="16">
         <v>220</v>
       </c>
-      <c r="N151" s="43">
+      <c r="N151" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>820</v>
       </c>
-      <c r="O151" s="56">
+      <c r="O151" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -27612,11 +28038,11 @@
       <c r="M152" s="17">
         <v>600</v>
       </c>
-      <c r="N152" s="43">
+      <c r="N152" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1550</v>
       </c>
-      <c r="O152" s="56">
+      <c r="O152" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -27662,11 +28088,11 @@
       <c r="M153" s="16">
         <v>220</v>
       </c>
-      <c r="N153" s="43">
+      <c r="N153" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>670</v>
       </c>
-      <c r="O153" s="56">
+      <c r="O153" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -27712,11 +28138,11 @@
       <c r="M154" s="17">
         <v>310</v>
       </c>
-      <c r="N154" s="43">
+      <c r="N154" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>660</v>
       </c>
-      <c r="O154" s="56">
+      <c r="O154" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -27762,11 +28188,11 @@
       <c r="M155" s="16">
         <v>350</v>
       </c>
-      <c r="N155" s="43">
+      <c r="N155" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1100</v>
       </c>
-      <c r="O155" s="56">
+      <c r="O155" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -27812,11 +28238,11 @@
       <c r="M156" s="17">
         <v>160</v>
       </c>
-      <c r="N156" s="43">
+      <c r="N156" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>510</v>
       </c>
-      <c r="O156" s="56">
+      <c r="O156" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -27862,11 +28288,11 @@
       <c r="M157" s="16">
         <v>200</v>
       </c>
-      <c r="N157" s="43">
+      <c r="N157" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>700</v>
       </c>
-      <c r="O157" s="56">
+      <c r="O157" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -27912,11 +28338,11 @@
       <c r="M158" s="17">
         <v>160</v>
       </c>
-      <c r="N158" s="43">
+      <c r="N158" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>610</v>
       </c>
-      <c r="O158" s="56">
+      <c r="O158" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -27962,11 +28388,11 @@
       <c r="M159" s="16">
         <v>200</v>
       </c>
-      <c r="N159" s="43">
+      <c r="N159" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>850</v>
       </c>
-      <c r="O159" s="56">
+      <c r="O159" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -28012,11 +28438,11 @@
       <c r="M160" s="17">
         <v>440</v>
       </c>
-      <c r="N160" s="43">
+      <c r="N160" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1140</v>
       </c>
-      <c r="O160" s="56">
+      <c r="O160" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -28062,11 +28488,11 @@
       <c r="M161" s="16">
         <v>110</v>
       </c>
-      <c r="N161" s="43">
+      <c r="N161" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>610</v>
       </c>
-      <c r="O161" s="56">
+      <c r="O161" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -28112,11 +28538,11 @@
       <c r="M162" s="17">
         <v>480</v>
       </c>
-      <c r="N162" s="43">
+      <c r="N162" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1480</v>
       </c>
-      <c r="O162" s="56">
+      <c r="O162" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -28162,11 +28588,11 @@
       <c r="M163" s="16">
         <v>350</v>
       </c>
-      <c r="N163" s="43">
+      <c r="N163" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1200</v>
       </c>
-      <c r="O163" s="56">
+      <c r="O163" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -28212,11 +28638,11 @@
       <c r="M164" s="17">
         <v>350</v>
       </c>
-      <c r="N164" s="43">
+      <c r="N164" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1200</v>
       </c>
-      <c r="O164" s="56">
+      <c r="O164" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -28262,11 +28688,11 @@
       <c r="M165" s="16">
         <v>250</v>
       </c>
-      <c r="N165" s="43">
+      <c r="N165" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>900</v>
       </c>
-      <c r="O165" s="56">
+      <c r="O165" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -28312,11 +28738,11 @@
       <c r="M166" s="17">
         <v>730</v>
       </c>
-      <c r="N166" s="43">
+      <c r="N166" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1580</v>
       </c>
-      <c r="O166" s="56">
+      <c r="O166" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -28362,11 +28788,11 @@
       <c r="M167" s="16">
         <v>460</v>
       </c>
-      <c r="N167" s="43">
+      <c r="N167" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1260</v>
       </c>
-      <c r="O167" s="56">
+      <c r="O167" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -28412,11 +28838,11 @@
       <c r="M168" s="17">
         <v>670</v>
       </c>
-      <c r="N168" s="43">
+      <c r="N168" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1520</v>
       </c>
-      <c r="O168" s="56">
+      <c r="O168" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -28462,11 +28888,11 @@
       <c r="M169" s="16">
         <v>680</v>
       </c>
-      <c r="N169" s="43">
+      <c r="N169" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1680</v>
       </c>
-      <c r="O169" s="56">
+      <c r="O169" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -28512,11 +28938,11 @@
       <c r="M170" s="17">
         <v>250</v>
       </c>
-      <c r="N170" s="43">
+      <c r="N170" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>650</v>
       </c>
-      <c r="O170" s="56">
+      <c r="O170" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -28562,11 +28988,11 @@
       <c r="M171" s="16">
         <v>360</v>
       </c>
-      <c r="N171" s="43">
+      <c r="N171" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>760</v>
       </c>
-      <c r="O171" s="56">
+      <c r="O171" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -28612,11 +29038,11 @@
       <c r="M172" s="17">
         <v>500</v>
       </c>
-      <c r="N172" s="43">
+      <c r="N172" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1600</v>
       </c>
-      <c r="O172" s="56">
+      <c r="O172" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -28662,11 +29088,11 @@
       <c r="M173" s="16">
         <v>680</v>
       </c>
-      <c r="N173" s="43">
+      <c r="N173" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1630</v>
       </c>
-      <c r="O173" s="56">
+      <c r="O173" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -28712,11 +29138,11 @@
       <c r="M174" s="17">
         <v>420</v>
       </c>
-      <c r="N174" s="43">
+      <c r="N174" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1220</v>
       </c>
-      <c r="O174" s="56">
+      <c r="O174" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -28762,11 +29188,11 @@
       <c r="M175" s="16">
         <v>230</v>
       </c>
-      <c r="N175" s="43">
+      <c r="N175" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>880</v>
       </c>
-      <c r="O175" s="56">
+      <c r="O175" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -28812,11 +29238,11 @@
       <c r="M176" s="17">
         <v>310</v>
       </c>
-      <c r="N176" s="43">
+      <c r="N176" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1060</v>
       </c>
-      <c r="O176" s="56">
+      <c r="O176" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -28862,11 +29288,11 @@
       <c r="M177" s="16">
         <v>330</v>
       </c>
-      <c r="N177" s="43">
+      <c r="N177" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>780</v>
       </c>
-      <c r="O177" s="56">
+      <c r="O177" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -28912,11 +29338,11 @@
       <c r="M178" s="17">
         <v>420</v>
       </c>
-      <c r="N178" s="43">
+      <c r="N178" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1070</v>
       </c>
-      <c r="O178" s="56">
+      <c r="O178" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -28962,11 +29388,11 @@
       <c r="M179" s="16">
         <v>100</v>
       </c>
-      <c r="N179" s="43">
+      <c r="N179" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>500</v>
       </c>
-      <c r="O179" s="56">
+      <c r="O179" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -29012,11 +29438,11 @@
       <c r="M180" s="17">
         <v>840</v>
       </c>
-      <c r="N180" s="43">
+      <c r="N180" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1640</v>
       </c>
-      <c r="O180" s="56">
+      <c r="O180" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -29062,11 +29488,11 @@
       <c r="M181" s="16">
         <v>130</v>
       </c>
-      <c r="N181" s="43">
+      <c r="N181" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>630</v>
       </c>
-      <c r="O181" s="56">
+      <c r="O181" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -29112,11 +29538,11 @@
       <c r="M182" s="17">
         <v>640</v>
       </c>
-      <c r="N182" s="43">
+      <c r="N182" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1390</v>
       </c>
-      <c r="O182" s="56">
+      <c r="O182" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -29162,11 +29588,11 @@
       <c r="M183" s="16">
         <v>190</v>
       </c>
-      <c r="N183" s="43">
+      <c r="N183" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>640</v>
       </c>
-      <c r="O183" s="56">
+      <c r="O183" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -29212,11 +29638,11 @@
       <c r="M184" s="17">
         <v>180</v>
       </c>
-      <c r="N184" s="43">
+      <c r="N184" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>980</v>
       </c>
-      <c r="O184" s="56">
+      <c r="O184" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -29262,11 +29688,11 @@
       <c r="M185" s="16">
         <v>370</v>
       </c>
-      <c r="N185" s="43">
+      <c r="N185" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>670</v>
       </c>
-      <c r="O185" s="56">
+      <c r="O185" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -29312,11 +29738,11 @@
       <c r="M186" s="17">
         <v>600</v>
       </c>
-      <c r="N186" s="43">
+      <c r="N186" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1750</v>
       </c>
-      <c r="O186" s="56">
+      <c r="O186" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -29362,11 +29788,11 @@
       <c r="M187" s="16">
         <v>220</v>
       </c>
-      <c r="N187" s="43">
+      <c r="N187" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>820</v>
       </c>
-      <c r="O187" s="56">
+      <c r="O187" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -29412,11 +29838,11 @@
       <c r="M188" s="17">
         <v>480</v>
       </c>
-      <c r="N188" s="43">
+      <c r="N188" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1330</v>
       </c>
-      <c r="O188" s="56">
+      <c r="O188" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -29462,11 +29888,11 @@
       <c r="M189" s="16">
         <v>180</v>
       </c>
-      <c r="N189" s="43">
+      <c r="N189" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>580</v>
       </c>
-      <c r="O189" s="56">
+      <c r="O189" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -29512,11 +29938,11 @@
       <c r="M190" s="17">
         <v>190</v>
       </c>
-      <c r="N190" s="43">
+      <c r="N190" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>640</v>
       </c>
-      <c r="O190" s="56">
+      <c r="O190" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -29562,11 +29988,11 @@
       <c r="M191" s="16">
         <v>790</v>
       </c>
-      <c r="N191" s="43">
+      <c r="N191" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1840</v>
       </c>
-      <c r="O191" s="56">
+      <c r="O191" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -29612,11 +30038,11 @@
       <c r="M192" s="17">
         <v>310</v>
       </c>
-      <c r="N192" s="43">
+      <c r="N192" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>660</v>
       </c>
-      <c r="O192" s="56">
+      <c r="O192" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -29662,11 +30088,11 @@
       <c r="M193" s="16">
         <v>600</v>
       </c>
-      <c r="N193" s="43">
+      <c r="N193" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1550</v>
       </c>
-      <c r="O193" s="56">
+      <c r="O193" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -29712,11 +30138,11 @@
       <c r="M194" s="17">
         <v>480</v>
       </c>
-      <c r="N194" s="43">
+      <c r="N194" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1530</v>
       </c>
-      <c r="O194" s="56">
+      <c r="O194" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -29762,11 +30188,11 @@
       <c r="M195" s="16">
         <v>600</v>
       </c>
-      <c r="N195" s="43">
+      <c r="N195" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1500</v>
       </c>
-      <c r="O195" s="56">
+      <c r="O195" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -29812,11 +30238,11 @@
       <c r="M196" s="17">
         <v>350</v>
       </c>
-      <c r="N196" s="43">
+      <c r="N196" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>750</v>
       </c>
-      <c r="O196" s="56">
+      <c r="O196" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -29862,11 +30288,11 @@
       <c r="M197" s="16">
         <v>310</v>
       </c>
-      <c r="N197" s="43">
+      <c r="N197" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>810</v>
       </c>
-      <c r="O197" s="56">
+      <c r="O197" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -29912,11 +30338,11 @@
       <c r="M198" s="17">
         <v>230</v>
       </c>
-      <c r="N198" s="43">
+      <c r="N198" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1130</v>
       </c>
-      <c r="O198" s="56">
+      <c r="O198" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -29962,11 +30388,11 @@
       <c r="M199" s="16">
         <v>320</v>
       </c>
-      <c r="N199" s="43">
+      <c r="N199" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>920</v>
       </c>
-      <c r="O199" s="56">
+      <c r="O199" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -30012,11 +30438,11 @@
       <c r="M200" s="17">
         <v>290</v>
       </c>
-      <c r="N200" s="43">
+      <c r="N200" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1140</v>
       </c>
-      <c r="O200" s="56">
+      <c r="O200" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -30062,11 +30488,11 @@
       <c r="M201" s="16">
         <v>300</v>
       </c>
-      <c r="N201" s="43">
+      <c r="N201" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>700</v>
       </c>
-      <c r="O201" s="56">
+      <c r="O201" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -30112,11 +30538,11 @@
       <c r="M202" s="17">
         <v>210</v>
       </c>
-      <c r="N202" s="43">
+      <c r="N202" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>860</v>
       </c>
-      <c r="O202" s="56">
+      <c r="O202" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -30162,11 +30588,11 @@
       <c r="M203" s="16">
         <v>240</v>
       </c>
-      <c r="N203" s="43">
+      <c r="N203" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1040</v>
       </c>
-      <c r="O203" s="56">
+      <c r="O203" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -30212,11 +30638,11 @@
       <c r="M204" s="17">
         <v>210</v>
       </c>
-      <c r="N204" s="43">
+      <c r="N204" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>810</v>
       </c>
-      <c r="O204" s="56">
+      <c r="O204" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -30262,11 +30688,11 @@
       <c r="M205" s="16">
         <v>820</v>
       </c>
-      <c r="N205" s="43">
+      <c r="N205" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1820</v>
       </c>
-      <c r="O205" s="56">
+      <c r="O205" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -30312,11 +30738,11 @@
       <c r="M206" s="17">
         <v>480</v>
       </c>
-      <c r="N206" s="43">
+      <c r="N206" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1180</v>
       </c>
-      <c r="O206" s="56">
+      <c r="O206" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -30362,11 +30788,11 @@
       <c r="M207" s="16">
         <v>600</v>
       </c>
-      <c r="N207" s="43">
+      <c r="N207" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1450</v>
       </c>
-      <c r="O207" s="56">
+      <c r="O207" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -30412,11 +30838,11 @@
       <c r="M208" s="17">
         <v>120</v>
       </c>
-      <c r="N208" s="43">
+      <c r="N208" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>570</v>
       </c>
-      <c r="O208" s="56">
+      <c r="O208" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -30462,11 +30888,11 @@
       <c r="M209" s="16">
         <v>820</v>
       </c>
-      <c r="N209" s="43">
+      <c r="N209" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1820</v>
       </c>
-      <c r="O209" s="56">
+      <c r="O209" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -30512,11 +30938,11 @@
       <c r="M210" s="17">
         <v>500</v>
       </c>
-      <c r="N210" s="43">
+      <c r="N210" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1200</v>
       </c>
-      <c r="O210" s="56">
+      <c r="O210" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -30562,11 +30988,11 @@
       <c r="M211" s="16">
         <v>400</v>
       </c>
-      <c r="N211" s="43">
+      <c r="N211" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>850</v>
       </c>
-      <c r="O211" s="56">
+      <c r="O211" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -30612,11 +31038,11 @@
       <c r="M212" s="17">
         <v>220</v>
       </c>
-      <c r="N212" s="43">
+      <c r="N212" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>970</v>
       </c>
-      <c r="O212" s="56">
+      <c r="O212" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -30662,11 +31088,11 @@
       <c r="M213" s="16">
         <v>160</v>
       </c>
-      <c r="N213" s="43">
+      <c r="N213" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>760</v>
       </c>
-      <c r="O213" s="56">
+      <c r="O213" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -30712,11 +31138,11 @@
       <c r="M214" s="17">
         <v>260</v>
       </c>
-      <c r="N214" s="43">
+      <c r="N214" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>810</v>
       </c>
-      <c r="O214" s="56">
+      <c r="O214" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -30762,11 +31188,11 @@
       <c r="M215" s="16">
         <v>320</v>
       </c>
-      <c r="N215" s="43">
+      <c r="N215" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>720</v>
       </c>
-      <c r="O215" s="56">
+      <c r="O215" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -30812,11 +31238,11 @@
       <c r="M216" s="17">
         <v>210</v>
       </c>
-      <c r="N216" s="43">
+      <c r="N216" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>710</v>
       </c>
-      <c r="O216" s="56">
+      <c r="O216" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -30862,11 +31288,11 @@
       <c r="M217" s="16">
         <v>340</v>
       </c>
-      <c r="N217" s="43">
+      <c r="N217" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>740</v>
       </c>
-      <c r="O217" s="56">
+      <c r="O217" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -30912,11 +31338,11 @@
       <c r="M218" s="17">
         <v>360</v>
       </c>
-      <c r="N218" s="43">
+      <c r="N218" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>760</v>
       </c>
-      <c r="O218" s="56">
+      <c r="O218" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -30962,11 +31388,11 @@
       <c r="M219" s="16">
         <v>210</v>
       </c>
-      <c r="N219" s="43">
+      <c r="N219" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>660</v>
       </c>
-      <c r="O219" s="56">
+      <c r="O219" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -31012,11 +31438,11 @@
       <c r="M220" s="17">
         <v>130</v>
       </c>
-      <c r="N220" s="43">
+      <c r="N220" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>480</v>
       </c>
-      <c r="O220" s="56">
+      <c r="O220" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -31062,11 +31488,11 @@
       <c r="M221" s="16">
         <v>140</v>
       </c>
-      <c r="N221" s="43">
+      <c r="N221" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>590</v>
       </c>
-      <c r="O221" s="56">
+      <c r="O221" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -31112,11 +31538,11 @@
       <c r="M222" s="17">
         <v>320</v>
       </c>
-      <c r="N222" s="43">
+      <c r="N222" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1020</v>
       </c>
-      <c r="O222" s="56">
+      <c r="O222" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -31162,11 +31588,11 @@
       <c r="M223" s="16">
         <v>500</v>
       </c>
-      <c r="N223" s="43">
+      <c r="N223" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1250</v>
       </c>
-      <c r="O223" s="56">
+      <c r="O223" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -31212,11 +31638,11 @@
       <c r="M224" s="17">
         <v>590</v>
       </c>
-      <c r="N224" s="43">
+      <c r="N224" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1490</v>
       </c>
-      <c r="O224" s="56">
+      <c r="O224" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -31262,11 +31688,11 @@
       <c r="M225" s="16">
         <v>230</v>
       </c>
-      <c r="N225" s="43">
+      <c r="N225" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1230</v>
       </c>
-      <c r="O225" s="56">
+      <c r="O225" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -31312,11 +31738,11 @@
       <c r="M226" s="17">
         <v>120</v>
       </c>
-      <c r="N226" s="43">
+      <c r="N226" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>570</v>
       </c>
-      <c r="O226" s="56">
+      <c r="O226" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -31362,11 +31788,11 @@
       <c r="M227" s="16">
         <v>480</v>
       </c>
-      <c r="N227" s="43">
+      <c r="N227" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1530</v>
       </c>
-      <c r="O227" s="56">
+      <c r="O227" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -31412,11 +31838,11 @@
       <c r="M228" s="17">
         <v>230</v>
       </c>
-      <c r="N228" s="43">
+      <c r="N228" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>730</v>
       </c>
-      <c r="O228" s="56">
+      <c r="O228" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -31462,11 +31888,11 @@
       <c r="M229" s="16">
         <v>140</v>
       </c>
-      <c r="N229" s="43">
+      <c r="N229" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>840</v>
       </c>
-      <c r="O229" s="56">
+      <c r="O229" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -31512,11 +31938,11 @@
       <c r="M230" s="17">
         <v>330</v>
       </c>
-      <c r="N230" s="43">
+      <c r="N230" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>680</v>
       </c>
-      <c r="O230" s="56">
+      <c r="O230" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -31562,11 +31988,11 @@
       <c r="M231" s="16">
         <v>400</v>
       </c>
-      <c r="N231" s="43">
+      <c r="N231" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1400</v>
       </c>
-      <c r="O231" s="56">
+      <c r="O231" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -31612,11 +32038,11 @@
       <c r="M232" s="17">
         <v>240</v>
       </c>
-      <c r="N232" s="43">
+      <c r="N232" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>790</v>
       </c>
-      <c r="O232" s="56">
+      <c r="O232" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -31662,11 +32088,11 @@
       <c r="M233" s="16">
         <v>680</v>
       </c>
-      <c r="N233" s="43">
+      <c r="N233" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1680</v>
       </c>
-      <c r="O233" s="56">
+      <c r="O233" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -31712,11 +32138,11 @@
       <c r="M234" s="17">
         <v>340</v>
       </c>
-      <c r="N234" s="43">
+      <c r="N234" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>640</v>
       </c>
-      <c r="O234" s="56">
+      <c r="O234" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -31762,11 +32188,11 @@
       <c r="M235" s="16">
         <v>100</v>
       </c>
-      <c r="N235" s="43">
+      <c r="N235" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>500</v>
       </c>
-      <c r="O235" s="56">
+      <c r="O235" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -31812,11 +32238,11 @@
       <c r="M236" s="17">
         <v>340</v>
       </c>
-      <c r="N236" s="43">
+      <c r="N236" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>690</v>
       </c>
-      <c r="O236" s="56">
+      <c r="O236" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -31862,11 +32288,11 @@
       <c r="M237" s="16">
         <v>360</v>
       </c>
-      <c r="N237" s="43">
+      <c r="N237" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>810</v>
       </c>
-      <c r="O237" s="56">
+      <c r="O237" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -31912,11 +32338,11 @@
       <c r="M238" s="17">
         <v>570</v>
       </c>
-      <c r="N238" s="43">
+      <c r="N238" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1470</v>
       </c>
-      <c r="O238" s="56">
+      <c r="O238" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -31962,11 +32388,11 @@
       <c r="M239" s="16">
         <v>190</v>
       </c>
-      <c r="N239" s="43">
+      <c r="N239" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>540</v>
       </c>
-      <c r="O239" s="56">
+      <c r="O239" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -32012,11 +32438,11 @@
       <c r="M240" s="17">
         <v>360</v>
       </c>
-      <c r="N240" s="43">
+      <c r="N240" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>710</v>
       </c>
-      <c r="O240" s="56">
+      <c r="O240" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -32062,11 +32488,11 @@
       <c r="M241" s="16">
         <v>220</v>
       </c>
-      <c r="N241" s="43">
+      <c r="N241" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>870</v>
       </c>
-      <c r="O241" s="56">
+      <c r="O241" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -32112,11 +32538,11 @@
       <c r="M242" s="17">
         <v>120</v>
       </c>
-      <c r="N242" s="43">
+      <c r="N242" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>420</v>
       </c>
-      <c r="O242" s="56">
+      <c r="O242" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -32162,11 +32588,11 @@
       <c r="M243" s="16">
         <v>190</v>
       </c>
-      <c r="N243" s="43">
+      <c r="N243" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>540</v>
       </c>
-      <c r="O243" s="56">
+      <c r="O243" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -32212,11 +32638,11 @@
       <c r="M244" s="17">
         <v>690</v>
       </c>
-      <c r="N244" s="43">
+      <c r="N244" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1540</v>
       </c>
-      <c r="O244" s="56">
+      <c r="O244" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -32262,11 +32688,11 @@
       <c r="M245" s="16">
         <v>480</v>
       </c>
-      <c r="N245" s="43">
+      <c r="N245" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1030</v>
       </c>
-      <c r="O245" s="56">
+      <c r="O245" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -32312,11 +32738,11 @@
       <c r="M246" s="17">
         <v>730</v>
       </c>
-      <c r="N246" s="43">
+      <c r="N246" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1580</v>
       </c>
-      <c r="O246" s="56">
+      <c r="O246" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -32362,11 +32788,11 @@
       <c r="M247" s="16">
         <v>190</v>
       </c>
-      <c r="N247" s="43">
+      <c r="N247" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>590</v>
       </c>
-      <c r="O247" s="56">
+      <c r="O247" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -32412,11 +32838,11 @@
       <c r="M248" s="17">
         <v>650</v>
       </c>
-      <c r="N248" s="43">
+      <c r="N248" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1400</v>
       </c>
-      <c r="O248" s="56">
+      <c r="O248" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -32462,11 +32888,11 @@
       <c r="M249" s="16">
         <v>280</v>
       </c>
-      <c r="N249" s="43">
+      <c r="N249" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>880</v>
       </c>
-      <c r="O249" s="56">
+      <c r="O249" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -32512,11 +32938,11 @@
       <c r="M250" s="17">
         <v>240</v>
       </c>
-      <c r="N250" s="43">
+      <c r="N250" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>740</v>
       </c>
-      <c r="O250" s="56">
+      <c r="O250" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -32562,11 +32988,11 @@
       <c r="M251" s="16">
         <v>190</v>
       </c>
-      <c r="N251" s="43">
+      <c r="N251" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1040</v>
       </c>
-      <c r="O251" s="56">
+      <c r="O251" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -32612,11 +33038,11 @@
       <c r="M252" s="17">
         <v>380</v>
       </c>
-      <c r="N252" s="43">
+      <c r="N252" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1130</v>
       </c>
-      <c r="O252" s="56">
+      <c r="O252" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -32662,11 +33088,11 @@
       <c r="M253" s="16">
         <v>370</v>
       </c>
-      <c r="N253" s="43">
+      <c r="N253" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1520</v>
       </c>
-      <c r="O253" s="56">
+      <c r="O253" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -32712,11 +33138,11 @@
       <c r="M254" s="17">
         <v>490</v>
       </c>
-      <c r="N254" s="43">
+      <c r="N254" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1490</v>
       </c>
-      <c r="O254" s="56">
+      <c r="O254" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -32762,11 +33188,11 @@
       <c r="M255" s="16">
         <v>260</v>
       </c>
-      <c r="N255" s="43">
+      <c r="N255" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>660</v>
       </c>
-      <c r="O255" s="56">
+      <c r="O255" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -32812,11 +33238,11 @@
       <c r="M256" s="17">
         <v>380</v>
       </c>
-      <c r="N256" s="43">
+      <c r="N256" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>880</v>
       </c>
-      <c r="O256" s="56">
+      <c r="O256" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -32862,11 +33288,11 @@
       <c r="M257" s="16">
         <v>640</v>
       </c>
-      <c r="N257" s="43">
+      <c r="N257" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1490</v>
       </c>
-      <c r="O257" s="56">
+      <c r="O257" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -32912,11 +33338,11 @@
       <c r="M258" s="17">
         <v>450</v>
       </c>
-      <c r="N258" s="43">
+      <c r="N258" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1250</v>
       </c>
-      <c r="O258" s="56">
+      <c r="O258" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -32962,11 +33388,11 @@
       <c r="M259" s="16">
         <v>160</v>
       </c>
-      <c r="N259" s="43">
+      <c r="N259" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>460</v>
       </c>
-      <c r="O259" s="56">
+      <c r="O259" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -33012,11 +33438,11 @@
       <c r="M260" s="17">
         <v>190</v>
       </c>
-      <c r="N260" s="43">
+      <c r="N260" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>540</v>
       </c>
-      <c r="O260" s="56">
+      <c r="O260" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -33062,11 +33488,11 @@
       <c r="M261" s="16">
         <v>370</v>
       </c>
-      <c r="N261" s="43">
+      <c r="N261" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1020</v>
       </c>
-      <c r="O261" s="56">
+      <c r="O261" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -33112,11 +33538,11 @@
       <c r="M262" s="17">
         <v>100</v>
       </c>
-      <c r="N262" s="43">
+      <c r="N262" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>450</v>
       </c>
-      <c r="O262" s="56">
+      <c r="O262" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -33162,11 +33588,11 @@
       <c r="M263" s="16">
         <v>760</v>
       </c>
-      <c r="N263" s="43">
+      <c r="N263" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1910</v>
       </c>
-      <c r="O263" s="56">
+      <c r="O263" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -33212,11 +33638,11 @@
       <c r="M264" s="17">
         <v>490</v>
       </c>
-      <c r="N264" s="43">
+      <c r="N264" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1090</v>
       </c>
-      <c r="O264" s="56">
+      <c r="O264" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -33262,11 +33688,11 @@
       <c r="M265" s="16">
         <v>780</v>
       </c>
-      <c r="N265" s="43">
+      <c r="N265" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1830</v>
       </c>
-      <c r="O265" s="56">
+      <c r="O265" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -33312,11 +33738,11 @@
       <c r="M266" s="17">
         <v>220</v>
       </c>
-      <c r="N266" s="43">
+      <c r="N266" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>520</v>
       </c>
-      <c r="O266" s="56">
+      <c r="O266" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -33362,11 +33788,11 @@
       <c r="M267" s="16">
         <v>160</v>
       </c>
-      <c r="N267" s="43">
+      <c r="N267" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>510</v>
       </c>
-      <c r="O267" s="56">
+      <c r="O267" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -33412,11 +33838,11 @@
       <c r="M268" s="17">
         <v>660</v>
       </c>
-      <c r="N268" s="43">
+      <c r="N268" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1610</v>
       </c>
-      <c r="O268" s="56">
+      <c r="O268" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -33462,11 +33888,11 @@
       <c r="M269" s="16">
         <v>250</v>
       </c>
-      <c r="N269" s="43">
+      <c r="N269" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>600</v>
       </c>
-      <c r="O269" s="56">
+      <c r="O269" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -33512,11 +33938,11 @@
       <c r="M270" s="17">
         <v>500</v>
       </c>
-      <c r="N270" s="43">
+      <c r="N270" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1100</v>
       </c>
-      <c r="O270" s="56">
+      <c r="O270" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -33562,11 +33988,11 @@
       <c r="M271" s="16">
         <v>400</v>
       </c>
-      <c r="N271" s="43">
+      <c r="N271" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1000</v>
       </c>
-      <c r="O271" s="56">
+      <c r="O271" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -33612,11 +34038,11 @@
       <c r="M272" s="17">
         <v>610</v>
       </c>
-      <c r="N272" s="43">
+      <c r="N272" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1610</v>
       </c>
-      <c r="O272" s="56">
+      <c r="O272" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -33662,11 +34088,11 @@
       <c r="M273" s="16">
         <v>760</v>
       </c>
-      <c r="N273" s="43">
+      <c r="N273" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1910</v>
       </c>
-      <c r="O273" s="56">
+      <c r="O273" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -33712,11 +34138,11 @@
       <c r="M274" s="17">
         <v>430</v>
       </c>
-      <c r="N274" s="43">
+      <c r="N274" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1480</v>
       </c>
-      <c r="O274" s="56">
+      <c r="O274" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -33762,11 +34188,11 @@
       <c r="M275" s="16">
         <v>230</v>
       </c>
-      <c r="N275" s="43">
+      <c r="N275" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>880</v>
       </c>
-      <c r="O275" s="56">
+      <c r="O275" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -33812,11 +34238,11 @@
       <c r="M276" s="17">
         <v>300</v>
       </c>
-      <c r="N276" s="43">
+      <c r="N276" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1100</v>
       </c>
-      <c r="O276" s="56">
+      <c r="O276" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -33862,11 +34288,11 @@
       <c r="M277" s="16">
         <v>140</v>
       </c>
-      <c r="N277" s="43">
+      <c r="N277" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>540</v>
       </c>
-      <c r="O277" s="56">
+      <c r="O277" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -33912,11 +34338,11 @@
       <c r="M278" s="17">
         <v>750</v>
       </c>
-      <c r="N278" s="43">
+      <c r="N278" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1700</v>
       </c>
-      <c r="O278" s="56">
+      <c r="O278" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -33962,11 +34388,11 @@
       <c r="M279" s="16">
         <v>460</v>
       </c>
-      <c r="N279" s="43">
+      <c r="N279" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1160</v>
       </c>
-      <c r="O279" s="56">
+      <c r="O279" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -34012,11 +34438,11 @@
       <c r="M280" s="17">
         <v>400</v>
       </c>
-      <c r="N280" s="43">
+      <c r="N280" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1100</v>
       </c>
-      <c r="O280" s="56">
+      <c r="O280" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -34062,11 +34488,11 @@
       <c r="M281" s="16">
         <v>140</v>
       </c>
-      <c r="N281" s="43">
+      <c r="N281" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>840</v>
       </c>
-      <c r="O281" s="56">
+      <c r="O281" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -34112,11 +34538,11 @@
       <c r="M282" s="17">
         <v>110</v>
       </c>
-      <c r="N282" s="43">
+      <c r="N282" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>660</v>
       </c>
-      <c r="O282" s="56">
+      <c r="O282" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -34162,11 +34588,11 @@
       <c r="M283" s="16">
         <v>380</v>
       </c>
-      <c r="N283" s="43">
+      <c r="N283" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1030</v>
       </c>
-      <c r="O283" s="56">
+      <c r="O283" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -34212,11 +34638,11 @@
       <c r="M284" s="17">
         <v>340</v>
       </c>
-      <c r="N284" s="43">
+      <c r="N284" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>890</v>
       </c>
-      <c r="O284" s="56">
+      <c r="O284" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -34262,11 +34688,11 @@
       <c r="M285" s="16">
         <v>310</v>
       </c>
-      <c r="N285" s="43">
+      <c r="N285" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>710</v>
       </c>
-      <c r="O285" s="56">
+      <c r="O285" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -34312,11 +34738,11 @@
       <c r="M286" s="17">
         <v>260</v>
       </c>
-      <c r="N286" s="43">
+      <c r="N286" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1160</v>
       </c>
-      <c r="O286" s="56">
+      <c r="O286" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -34362,11 +34788,11 @@
       <c r="M287" s="16">
         <v>430</v>
       </c>
-      <c r="N287" s="43">
+      <c r="N287" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1030</v>
       </c>
-      <c r="O287" s="56">
+      <c r="O287" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -34412,11 +34838,11 @@
       <c r="M288" s="17">
         <v>440</v>
       </c>
-      <c r="N288" s="43">
+      <c r="N288" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1090</v>
       </c>
-      <c r="O288" s="56">
+      <c r="O288" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -34462,11 +34888,11 @@
       <c r="M289" s="16">
         <v>230</v>
       </c>
-      <c r="N289" s="43">
+      <c r="N289" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>580</v>
       </c>
-      <c r="O289" s="56">
+      <c r="O289" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -34512,11 +34938,11 @@
       <c r="M290" s="17">
         <v>280</v>
       </c>
-      <c r="N290" s="43">
+      <c r="N290" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>730</v>
       </c>
-      <c r="O290" s="56">
+      <c r="O290" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -34562,11 +34988,11 @@
       <c r="M291" s="16">
         <v>180</v>
       </c>
-      <c r="N291" s="43">
+      <c r="N291" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>530</v>
       </c>
-      <c r="O291" s="56">
+      <c r="O291" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -34612,11 +35038,11 @@
       <c r="M292" s="17">
         <v>270</v>
       </c>
-      <c r="N292" s="43">
+      <c r="N292" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>720</v>
       </c>
-      <c r="O292" s="56">
+      <c r="O292" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -34662,11 +35088,11 @@
       <c r="M293" s="16">
         <v>300</v>
       </c>
-      <c r="N293" s="43">
+      <c r="N293" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1050</v>
       </c>
-      <c r="O293" s="56">
+      <c r="O293" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -34712,11 +35138,11 @@
       <c r="M294" s="17">
         <v>700</v>
       </c>
-      <c r="N294" s="43">
+      <c r="N294" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1550</v>
       </c>
-      <c r="O294" s="56">
+      <c r="O294" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -34762,11 +35188,11 @@
       <c r="M295" s="16">
         <v>330</v>
       </c>
-      <c r="N295" s="43">
+      <c r="N295" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1180</v>
       </c>
-      <c r="O295" s="56">
+      <c r="O295" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -34812,11 +35238,11 @@
       <c r="M296" s="17">
         <v>190</v>
       </c>
-      <c r="N296" s="43">
+      <c r="N296" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>490</v>
       </c>
-      <c r="O296" s="56">
+      <c r="O296" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -34862,11 +35288,11 @@
       <c r="M297" s="16">
         <v>110</v>
       </c>
-      <c r="N297" s="43">
+      <c r="N297" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>610</v>
       </c>
-      <c r="O297" s="56">
+      <c r="O297" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -34912,11 +35338,11 @@
       <c r="M298" s="17">
         <v>420</v>
       </c>
-      <c r="N298" s="43">
+      <c r="N298" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1070</v>
       </c>
-      <c r="O298" s="56">
+      <c r="O298" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -34962,11 +35388,11 @@
       <c r="M299" s="16">
         <v>430</v>
       </c>
-      <c r="N299" s="43">
+      <c r="N299" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1180</v>
       </c>
-      <c r="O299" s="56">
+      <c r="O299" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -35012,11 +35438,11 @@
       <c r="M300" s="17">
         <v>120</v>
       </c>
-      <c r="N300" s="43">
+      <c r="N300" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>570</v>
       </c>
-      <c r="O300" s="56">
+      <c r="O300" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -35062,11 +35488,11 @@
       <c r="M301" s="16">
         <v>420</v>
       </c>
-      <c r="N301" s="43">
+      <c r="N301" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1120</v>
       </c>
-      <c r="O301" s="56">
+      <c r="O301" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -35112,11 +35538,11 @@
       <c r="M302" s="17">
         <v>560</v>
       </c>
-      <c r="N302" s="43">
+      <c r="N302" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1360</v>
       </c>
-      <c r="O302" s="56">
+      <c r="O302" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -35162,11 +35588,11 @@
       <c r="M303" s="16">
         <v>280</v>
       </c>
-      <c r="N303" s="43">
+      <c r="N303" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>730</v>
       </c>
-      <c r="O303" s="56">
+      <c r="O303" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -35212,11 +35638,11 @@
       <c r="M304" s="17">
         <v>290</v>
       </c>
-      <c r="N304" s="43">
+      <c r="N304" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>690</v>
       </c>
-      <c r="O304" s="56">
+      <c r="O304" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -35262,11 +35688,11 @@
       <c r="M305" s="16">
         <v>310</v>
       </c>
-      <c r="N305" s="43">
+      <c r="N305" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1060</v>
       </c>
-      <c r="O305" s="56">
+      <c r="O305" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -35312,11 +35738,11 @@
       <c r="M306" s="17">
         <v>240</v>
       </c>
-      <c r="N306" s="43">
+      <c r="N306" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>840</v>
       </c>
-      <c r="O306" s="56">
+      <c r="O306" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -35362,11 +35788,11 @@
       <c r="M307" s="16">
         <v>200</v>
       </c>
-      <c r="N307" s="43">
+      <c r="N307" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>900</v>
       </c>
-      <c r="O307" s="56">
+      <c r="O307" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -35412,11 +35838,11 @@
       <c r="M308" s="17">
         <v>230</v>
       </c>
-      <c r="N308" s="43">
+      <c r="N308" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>980</v>
       </c>
-      <c r="O308" s="56">
+      <c r="O308" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -35462,11 +35888,11 @@
       <c r="M309" s="16">
         <v>280</v>
       </c>
-      <c r="N309" s="43">
+      <c r="N309" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>880</v>
       </c>
-      <c r="O309" s="56">
+      <c r="O309" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -35512,11 +35938,11 @@
       <c r="M310" s="17">
         <v>330</v>
       </c>
-      <c r="N310" s="43">
+      <c r="N310" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>980</v>
       </c>
-      <c r="O310" s="56">
+      <c r="O310" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -35562,11 +35988,11 @@
       <c r="M311" s="16">
         <v>630</v>
       </c>
-      <c r="N311" s="43">
+      <c r="N311" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1780</v>
       </c>
-      <c r="O311" s="56">
+      <c r="O311" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -35612,11 +36038,11 @@
       <c r="M312" s="17">
         <v>220</v>
       </c>
-      <c r="N312" s="43">
+      <c r="N312" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>720</v>
       </c>
-      <c r="O312" s="56">
+      <c r="O312" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -35662,11 +36088,11 @@
       <c r="M313" s="16">
         <v>440</v>
       </c>
-      <c r="N313" s="43">
+      <c r="N313" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1340</v>
       </c>
-      <c r="O313" s="56">
+      <c r="O313" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -35712,11 +36138,11 @@
       <c r="M314" s="17">
         <v>800</v>
       </c>
-      <c r="N314" s="43">
+      <c r="N314" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1800</v>
       </c>
-      <c r="O314" s="56">
+      <c r="O314" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -35762,11 +36188,11 @@
       <c r="M315" s="16">
         <v>250</v>
       </c>
-      <c r="N315" s="43">
+      <c r="N315" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1250</v>
       </c>
-      <c r="O315" s="56">
+      <c r="O315" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -35812,11 +36238,11 @@
       <c r="M316" s="17">
         <v>340</v>
       </c>
-      <c r="N316" s="43">
+      <c r="N316" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1340</v>
       </c>
-      <c r="O316" s="56">
+      <c r="O316" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -35862,11 +36288,11 @@
       <c r="M317" s="16">
         <v>410</v>
       </c>
-      <c r="N317" s="43">
+      <c r="N317" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>910</v>
       </c>
-      <c r="O317" s="56">
+      <c r="O317" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -35912,11 +36338,11 @@
       <c r="M318" s="17">
         <v>760</v>
       </c>
-      <c r="N318" s="43">
+      <c r="N318" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1510</v>
       </c>
-      <c r="O318" s="56">
+      <c r="O318" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -35962,11 +36388,11 @@
       <c r="M319" s="16">
         <v>110</v>
       </c>
-      <c r="N319" s="43">
+      <c r="N319" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>460</v>
       </c>
-      <c r="O319" s="56">
+      <c r="O319" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -36012,11 +36438,11 @@
       <c r="M320" s="17">
         <v>220</v>
       </c>
-      <c r="N320" s="43">
+      <c r="N320" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>870</v>
       </c>
-      <c r="O320" s="56">
+      <c r="O320" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2023</v>
       </c>
@@ -36062,11 +36488,11 @@
       <c r="M321" s="16">
         <v>320</v>
       </c>
-      <c r="N321" s="43">
+      <c r="N321" s="27">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>1320</v>
       </c>
-      <c r="O321" s="56">
+      <c r="O321" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
@@ -36112,11 +36538,11 @@
       <c r="M322" s="22">
         <v>190</v>
       </c>
-      <c r="N322" s="45">
+      <c r="N322" s="29">
         <f>SUM(Table2[[#This Row],[Consultation Fee (₹)]],Table2[[#This Row],[Medicine Cost (₹)]])</f>
         <v>890</v>
       </c>
-      <c r="O322" s="56">
+      <c r="O322" s="39">
         <f>YEAR(Table2[[#This Row],[Visit Date]])</f>
         <v>2024</v>
       </c>
